--- a/research/traditional_assets/database/data/pakistan/pakistan_trucking.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_trucking.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1811537007128301</v>
+        <v>0.1806603049807629</v>
       </c>
       <c r="C2">
-        <v>17.86473452314461</v>
+        <v>17.75432437437682</v>
       </c>
       <c r="D2">
-        <v>17.84573452314461</v>
+        <v>17.91102437437682</v>
       </c>
       <c r="E2">
-        <v>-2.07</v>
+        <v>-1.8943</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1757</v>
       </c>
       <c r="G2">
         <v>0.019</v>
@@ -1433,28 +1433,28 @@
         <v>3.5175</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.008837709999999999</v>
       </c>
       <c r="N2">
-        <v>3.5175</v>
+        <v>3.50866229</v>
       </c>
       <c r="O2">
-        <v>1.020075</v>
+        <v>1.0175120641</v>
       </c>
       <c r="P2">
-        <v>2.497425</v>
+        <v>2.4911502259</v>
       </c>
       <c r="Q2">
-        <v>3.067425</v>
+        <v>3.0611502259</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1811537007128301</v>
+        <v>0.1821244191724878</v>
       </c>
       <c r="T2">
-        <v>0.8278063840919477</v>
+        <v>0.8337431773515971</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>398.0103443086501</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1806603049807629</v>
+        <v>0.1801669092486957</v>
       </c>
       <c r="C3">
-        <v>17.75432437437682</v>
+        <v>17.64439371470534</v>
       </c>
       <c r="D3">
-        <v>17.91102437437682</v>
+        <v>17.97679371470534</v>
       </c>
       <c r="E3">
-        <v>-1.8943</v>
+        <v>-1.7186</v>
       </c>
       <c r="F3">
-        <v>0.1757</v>
+        <v>0.3514</v>
       </c>
       <c r="G3">
         <v>0.019</v>
@@ -1515,28 +1515,28 @@
         <v>3.5175</v>
       </c>
       <c r="M3">
-        <v>0.008837709999999999</v>
+        <v>0.01767542</v>
       </c>
       <c r="N3">
-        <v>3.50866229</v>
+        <v>3.499824579999999</v>
       </c>
       <c r="O3">
-        <v>1.0175120641</v>
+        <v>1.0149491282</v>
       </c>
       <c r="P3">
-        <v>2.4911502259</v>
+        <v>2.4848754518</v>
       </c>
       <c r="Q3">
-        <v>3.0611502259</v>
+        <v>3.0548754518</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1821244191724878</v>
+        <v>0.1831149482129548</v>
       </c>
       <c r="T3">
-        <v>0.8337431773515971</v>
+        <v>0.8398011296573618</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>398.0103443086501</v>
+        <v>199.005172154325</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1801669092486957</v>
+        <v>0.1796735135166285</v>
       </c>
       <c r="C4">
-        <v>17.64439371470534</v>
+        <v>17.534947845654</v>
       </c>
       <c r="D4">
-        <v>17.97679371470534</v>
+        <v>18.043047845654</v>
       </c>
       <c r="E4">
-        <v>-1.7186</v>
+        <v>-1.5429</v>
       </c>
       <c r="F4">
-        <v>0.3514</v>
+        <v>0.5271</v>
       </c>
       <c r="G4">
         <v>0.019</v>
@@ -1597,28 +1597,28 @@
         <v>3.5175</v>
       </c>
       <c r="M4">
-        <v>0.01767542</v>
+        <v>0.02651313</v>
       </c>
       <c r="N4">
-        <v>3.499824579999999</v>
+        <v>3.49098687</v>
       </c>
       <c r="O4">
-        <v>1.0149491282</v>
+        <v>1.0123861923</v>
       </c>
       <c r="P4">
-        <v>2.4848754518</v>
+        <v>2.4786006777</v>
       </c>
       <c r="Q4">
-        <v>3.0548754518</v>
+        <v>3.0486006777</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1831149482129548</v>
+        <v>0.1841259005326067</v>
       </c>
       <c r="T4">
-        <v>0.8398011296573618</v>
+        <v>0.8459839881962349</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>199.005172154325</v>
+        <v>132.67011476955</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1796735135166285</v>
+        <v>0.1791801177845613</v>
       </c>
       <c r="C5">
-        <v>17.534947845654</v>
+        <v>17.42599214719159</v>
       </c>
       <c r="D5">
-        <v>18.043047845654</v>
+        <v>18.10979214719159</v>
       </c>
       <c r="E5">
-        <v>-1.5429</v>
+        <v>-1.3672</v>
       </c>
       <c r="F5">
-        <v>0.5271</v>
+        <v>0.7028</v>
       </c>
       <c r="G5">
         <v>0.019</v>
@@ -1679,28 +1679,28 @@
         <v>3.5175</v>
       </c>
       <c r="M5">
-        <v>0.02651313</v>
+        <v>0.03535083999999999</v>
       </c>
       <c r="N5">
-        <v>3.49098687</v>
+        <v>3.48214916</v>
       </c>
       <c r="O5">
-        <v>1.0123861923</v>
+        <v>1.0098232564</v>
       </c>
       <c r="P5">
-        <v>2.4786006777</v>
+        <v>2.4723259036</v>
       </c>
       <c r="Q5">
-        <v>3.0486006777</v>
+        <v>3.0423259036</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1841259005326067</v>
+        <v>0.185157914358918</v>
       </c>
       <c r="T5">
-        <v>0.8459839881962349</v>
+        <v>0.8522956562880012</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>132.67011476955</v>
+        <v>99.50258607716253</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1791801177845613</v>
+        <v>0.1786867220524941</v>
       </c>
       <c r="C6">
-        <v>17.42599214719159</v>
+        <v>17.31753207918809</v>
       </c>
       <c r="D6">
-        <v>18.10979214719159</v>
+        <v>18.17703207918809</v>
       </c>
       <c r="E6">
-        <v>-1.3672</v>
+        <v>-1.1915</v>
       </c>
       <c r="F6">
-        <v>0.7028</v>
+        <v>0.8785000000000001</v>
       </c>
       <c r="G6">
         <v>0.019</v>
@@ -1761,28 +1761,28 @@
         <v>3.5175</v>
       </c>
       <c r="M6">
-        <v>0.03535083999999999</v>
+        <v>0.04418855</v>
       </c>
       <c r="N6">
-        <v>3.48214916</v>
+        <v>3.47331145</v>
       </c>
       <c r="O6">
-        <v>1.0098232564</v>
+        <v>1.0072603205</v>
       </c>
       <c r="P6">
-        <v>2.4723259036</v>
+        <v>2.4660511295</v>
       </c>
       <c r="Q6">
-        <v>3.0423259036</v>
+        <v>3.0360511295</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.185157914358918</v>
+        <v>0.186211654792099</v>
       </c>
       <c r="T6">
-        <v>0.8522956562880012</v>
+        <v>0.858740201602752</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>99.50258607716253</v>
+        <v>79.60206886173002</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1786867220524941</v>
+        <v>0.1781933263204269</v>
       </c>
       <c r="C7">
-        <v>17.31753207918809</v>
+        <v>17.20957318290365</v>
       </c>
       <c r="D7">
-        <v>18.17703207918809</v>
+        <v>18.24477318290366</v>
       </c>
       <c r="E7">
-        <v>-1.1915</v>
+        <v>-1.0158</v>
       </c>
       <c r="F7">
-        <v>0.8785000000000001</v>
+        <v>1.0542</v>
       </c>
       <c r="G7">
         <v>0.019</v>
@@ -1843,28 +1843,28 @@
         <v>3.5175</v>
       </c>
       <c r="M7">
-        <v>0.04418855</v>
+        <v>0.05302626</v>
       </c>
       <c r="N7">
-        <v>3.47331145</v>
+        <v>3.464473739999999</v>
       </c>
       <c r="O7">
-        <v>1.0072603205</v>
+        <v>1.0046973846</v>
       </c>
       <c r="P7">
-        <v>2.4660511295</v>
+        <v>2.4597763554</v>
       </c>
       <c r="Q7">
-        <v>3.0360511295</v>
+        <v>3.0297763554</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.186211654792099</v>
+        <v>0.1872878152344967</v>
       </c>
       <c r="T7">
-        <v>0.858740201602752</v>
+        <v>0.8653218649029232</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>79.60206886173002</v>
+        <v>66.33505738477501</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1781933263204269</v>
+        <v>0.1776999305883597</v>
       </c>
       <c r="C8">
-        <v>17.20957318290365</v>
+        <v>17.10212108251076</v>
       </c>
       <c r="D8">
-        <v>18.24477318290366</v>
+        <v>18.31302108251076</v>
       </c>
       <c r="E8">
-        <v>-1.0158</v>
+        <v>-0.8400999999999998</v>
       </c>
       <c r="F8">
-        <v>1.0542</v>
+        <v>1.2299</v>
       </c>
       <c r="G8">
         <v>0.019</v>
@@ -1925,28 +1925,28 @@
         <v>3.5175</v>
       </c>
       <c r="M8">
-        <v>0.05302626</v>
+        <v>0.06186397</v>
       </c>
       <c r="N8">
-        <v>3.464473739999999</v>
+        <v>3.45563603</v>
       </c>
       <c r="O8">
-        <v>1.0046973846</v>
+        <v>1.0021344487</v>
       </c>
       <c r="P8">
-        <v>2.4597763554</v>
+        <v>2.453501581299999</v>
       </c>
       <c r="Q8">
-        <v>3.0297763554</v>
+        <v>3.023501581299999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1872878152344967</v>
+        <v>0.1883871189122147</v>
       </c>
       <c r="T8">
-        <v>0.8653218649029232</v>
+        <v>0.8720450693493347</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>66.33505738477501</v>
+        <v>56.85862061552144</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1776999305883597</v>
+        <v>0.1772065348562925</v>
       </c>
       <c r="C9">
-        <v>17.10212108251076</v>
+        <v>16.99518148665085</v>
       </c>
       <c r="D9">
-        <v>18.31302108251076</v>
+        <v>18.38178148665085</v>
       </c>
       <c r="E9">
-        <v>-0.8400999999999996</v>
+        <v>-0.6643999999999999</v>
       </c>
       <c r="F9">
-        <v>1.2299</v>
+        <v>1.4056</v>
       </c>
       <c r="G9">
         <v>0.019</v>
@@ -2007,28 +2007,28 @@
         <v>3.5175</v>
       </c>
       <c r="M9">
-        <v>0.06186397000000001</v>
+        <v>0.07070167999999999</v>
       </c>
       <c r="N9">
-        <v>3.45563603</v>
+        <v>3.44679832</v>
       </c>
       <c r="O9">
-        <v>1.0021344487</v>
+        <v>0.9995715127999998</v>
       </c>
       <c r="P9">
-        <v>2.453501581299999</v>
+        <v>2.4472268072</v>
       </c>
       <c r="Q9">
-        <v>3.023501581299999</v>
+        <v>3.0172268072</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1883871189122147</v>
+        <v>0.1895103204959701</v>
       </c>
       <c r="T9">
-        <v>0.8720450693493347</v>
+        <v>0.8789144304141462</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>56.85862061552142</v>
+        <v>49.75129303858127</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1772065348562925</v>
+        <v>0.1767131391242252</v>
       </c>
       <c r="C10">
-        <v>16.99518148665085</v>
+        <v>16.88876019002607</v>
       </c>
       <c r="D10">
-        <v>18.38178148665085</v>
+        <v>18.45106019002607</v>
       </c>
       <c r="E10">
-        <v>-0.6643999999999999</v>
+        <v>-0.4886999999999999</v>
       </c>
       <c r="F10">
-        <v>1.4056</v>
+        <v>1.5813</v>
       </c>
       <c r="G10">
         <v>0.019</v>
@@ -2089,28 +2089,28 @@
         <v>3.5175</v>
       </c>
       <c r="M10">
-        <v>0.07070167999999999</v>
+        <v>0.07953938999999999</v>
       </c>
       <c r="N10">
-        <v>3.44679832</v>
+        <v>3.43796061</v>
       </c>
       <c r="O10">
-        <v>0.9995715127999998</v>
+        <v>0.9970085768999999</v>
       </c>
       <c r="P10">
-        <v>2.4472268072</v>
+        <v>2.4409520331</v>
       </c>
       <c r="Q10">
-        <v>3.0172268072</v>
+        <v>3.0109520331</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1895103204959701</v>
+        <v>0.190658207828819</v>
       </c>
       <c r="T10">
-        <v>0.8789144304141462</v>
+        <v>0.8859347664474152</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>49.75129303858127</v>
+        <v>44.22337158985001</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1767131391242252</v>
+        <v>0.176219743392158</v>
       </c>
       <c r="C11">
-        <v>16.88876019002607</v>
+        <v>16.78286307502715</v>
       </c>
       <c r="D11">
-        <v>18.45106019002607</v>
+        <v>18.52086307502715</v>
       </c>
       <c r="E11">
-        <v>-0.4886999999999999</v>
+        <v>-0.3129999999999999</v>
       </c>
       <c r="F11">
-        <v>1.5813</v>
+        <v>1.757</v>
       </c>
       <c r="G11">
         <v>0.019</v>
@@ -2171,28 +2171,28 @@
         <v>3.5175</v>
       </c>
       <c r="M11">
-        <v>0.07953938999999999</v>
+        <v>0.08837709999999999</v>
       </c>
       <c r="N11">
-        <v>3.43796061</v>
+        <v>3.429122899999999</v>
       </c>
       <c r="O11">
-        <v>0.9970085768999999</v>
+        <v>0.9944456409999998</v>
       </c>
       <c r="P11">
-        <v>2.4409520331</v>
+        <v>2.434677259</v>
       </c>
       <c r="Q11">
-        <v>3.0109520331</v>
+        <v>3.004677259</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.190658207828819</v>
+        <v>0.1918316037690645</v>
       </c>
       <c r="T11">
-        <v>0.8859347664474152</v>
+        <v>0.8931111099480902</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>44.22337158985001</v>
+        <v>39.80103443086501</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.176219743392158</v>
+        <v>0.1757263476600908</v>
       </c>
       <c r="C12">
-        <v>16.78286307502715</v>
+        <v>16.67749611339844</v>
       </c>
       <c r="D12">
-        <v>18.52086307502715</v>
+        <v>18.59119611339845</v>
       </c>
       <c r="E12">
-        <v>-0.3129999999999997</v>
+        <v>-0.1372999999999998</v>
       </c>
       <c r="F12">
-        <v>1.757</v>
+        <v>1.9327</v>
       </c>
       <c r="G12">
         <v>0.019</v>
@@ -2253,28 +2253,28 @@
         <v>3.5175</v>
       </c>
       <c r="M12">
-        <v>0.0883771</v>
+        <v>0.09721481</v>
       </c>
       <c r="N12">
-        <v>3.429122899999999</v>
+        <v>3.42028519</v>
       </c>
       <c r="O12">
-        <v>0.9944456409999998</v>
+        <v>0.9918827050999998</v>
       </c>
       <c r="P12">
-        <v>2.434677259</v>
+        <v>2.4284024849</v>
       </c>
       <c r="Q12">
-        <v>3.004677259</v>
+        <v>2.9984024849</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1918316037690645</v>
+        <v>0.1930313681574054</v>
       </c>
       <c r="T12">
-        <v>0.8931111099480902</v>
+        <v>0.9004487195948478</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>39.801034430865</v>
+        <v>36.18275857351364</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1757263476600908</v>
+        <v>0.1752329519280236</v>
       </c>
       <c r="C13">
-        <v>16.67749611339844</v>
+        <v>16.57266536794095</v>
       </c>
       <c r="D13">
-        <v>18.59119611339845</v>
+        <v>18.66206536794095</v>
       </c>
       <c r="E13">
-        <v>-0.1372999999999998</v>
+        <v>0.03840000000000021</v>
       </c>
       <c r="F13">
-        <v>1.9327</v>
+        <v>2.1084</v>
       </c>
       <c r="G13">
         <v>0.019</v>
@@ -2335,28 +2335,28 @@
         <v>3.5175</v>
       </c>
       <c r="M13">
-        <v>0.09721481</v>
+        <v>0.10605252</v>
       </c>
       <c r="N13">
-        <v>3.42028519</v>
+        <v>3.41144748</v>
       </c>
       <c r="O13">
-        <v>0.9918827050999998</v>
+        <v>0.9893197691999999</v>
       </c>
       <c r="P13">
-        <v>2.4284024849</v>
+        <v>2.4221277108</v>
       </c>
       <c r="Q13">
-        <v>2.9984024849</v>
+        <v>2.9921277108</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1930313681574054</v>
+        <v>0.1942583999182087</v>
       </c>
       <c r="T13">
-        <v>0.9004487195948478</v>
+        <v>0.9079530930972135</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>36.18275857351364</v>
+        <v>33.16752869238751</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1752329519280236</v>
+        <v>0.1747395561959565</v>
       </c>
       <c r="C14">
-        <v>16.57266536794095</v>
+        <v>16.46837699425451</v>
       </c>
       <c r="D14">
-        <v>18.66206536794095</v>
+        <v>18.73347699425451</v>
       </c>
       <c r="E14">
-        <v>0.03840000000000021</v>
+        <v>0.2141000000000002</v>
       </c>
       <c r="F14">
-        <v>2.1084</v>
+        <v>2.2841</v>
       </c>
       <c r="G14">
         <v>0.019</v>
@@ -2417,28 +2417,28 @@
         <v>3.5175</v>
       </c>
       <c r="M14">
-        <v>0.10605252</v>
+        <v>0.11489023</v>
       </c>
       <c r="N14">
-        <v>3.41144748</v>
+        <v>3.40260977</v>
       </c>
       <c r="O14">
-        <v>0.9893197691999999</v>
+        <v>0.9867568332999999</v>
       </c>
       <c r="P14">
-        <v>2.4221277108</v>
+        <v>2.4158529367</v>
       </c>
       <c r="Q14">
-        <v>2.9921277108</v>
+        <v>2.9858529367</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1942583999182087</v>
+        <v>0.1955136393056971</v>
       </c>
       <c r="T14">
-        <v>0.9079530930972135</v>
+        <v>0.9156299809329671</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>33.16752869238751</v>
+        <v>30.61618033143462</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1747395561959565</v>
+        <v>0.1742461604638892</v>
       </c>
       <c r="C15">
-        <v>16.46837699425451</v>
+        <v>16.36463724252011</v>
       </c>
       <c r="D15">
-        <v>18.73347699425451</v>
+        <v>18.80543724252011</v>
       </c>
       <c r="E15">
-        <v>0.2141000000000002</v>
+        <v>0.3898000000000006</v>
       </c>
       <c r="F15">
-        <v>2.2841</v>
+        <v>2.4598</v>
       </c>
       <c r="G15">
         <v>0.019</v>
@@ -2499,28 +2499,28 @@
         <v>3.5175</v>
       </c>
       <c r="M15">
-        <v>0.11489023</v>
+        <v>0.12372794</v>
       </c>
       <c r="N15">
-        <v>3.40260977</v>
+        <v>3.393772059999999</v>
       </c>
       <c r="O15">
-        <v>0.9867568332999999</v>
+        <v>0.9841938973999997</v>
       </c>
       <c r="P15">
-        <v>2.4158529367</v>
+        <v>2.4095781626</v>
       </c>
       <c r="Q15">
-        <v>2.9858529367</v>
+        <v>2.9795781626</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1955136393056971</v>
+        <v>0.1967980703068479</v>
       </c>
       <c r="T15">
-        <v>0.9156299809329671</v>
+        <v>0.9234854010439705</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>30.61618033143462</v>
+        <v>28.42931030776071</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1742461604638892</v>
+        <v>0.173752764731822</v>
       </c>
       <c r="C16">
-        <v>16.36463724252011</v>
+        <v>16.26145245932347</v>
       </c>
       <c r="D16">
-        <v>18.80543724252011</v>
+        <v>18.87795245932347</v>
       </c>
       <c r="E16">
-        <v>0.3898000000000006</v>
+        <v>0.5655000000000006</v>
       </c>
       <c r="F16">
-        <v>2.4598</v>
+        <v>2.6355</v>
       </c>
       <c r="G16">
         <v>0.019</v>
@@ -2581,28 +2581,28 @@
         <v>3.5175</v>
       </c>
       <c r="M16">
-        <v>0.12372794</v>
+        <v>0.13256565</v>
       </c>
       <c r="N16">
-        <v>3.393772059999999</v>
+        <v>3.38493435</v>
       </c>
       <c r="O16">
-        <v>0.9841938973999997</v>
+        <v>0.9816309614999998</v>
       </c>
       <c r="P16">
-        <v>2.4095781626</v>
+        <v>2.403303388499999</v>
       </c>
       <c r="Q16">
-        <v>2.9795781626</v>
+        <v>2.973303388499999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1967980703068479</v>
+        <v>0.1981127232139082</v>
       </c>
       <c r="T16">
-        <v>0.9234854010439705</v>
+        <v>0.9315256545693505</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.42931030776071</v>
+        <v>26.53402295391</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.173752764731822</v>
+        <v>0.1732593689997548</v>
       </c>
       <c r="C17">
-        <v>16.26145245932347</v>
+        <v>16.15882908952094</v>
       </c>
       <c r="D17">
-        <v>18.87795245932347</v>
+        <v>18.95102908952094</v>
       </c>
       <c r="E17">
-        <v>0.5655000000000001</v>
+        <v>0.7412000000000001</v>
       </c>
       <c r="F17">
-        <v>2.6355</v>
+        <v>2.8112</v>
       </c>
       <c r="G17">
         <v>0.019</v>
@@ -2663,28 +2663,28 @@
         <v>3.5175</v>
       </c>
       <c r="M17">
-        <v>0.13256565</v>
+        <v>0.14140336</v>
       </c>
       <c r="N17">
-        <v>3.38493435</v>
+        <v>3.37609664</v>
       </c>
       <c r="O17">
-        <v>0.9816309614999998</v>
+        <v>0.9790680255999998</v>
       </c>
       <c r="P17">
-        <v>2.403303388499999</v>
+        <v>2.3970286144</v>
       </c>
       <c r="Q17">
-        <v>2.973303388499999</v>
+        <v>2.9670286144</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1981127232139082</v>
+        <v>0.1994586773806605</v>
       </c>
       <c r="T17">
-        <v>0.9315256545693505</v>
+        <v>0.9397573427024778</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>26.53402295391001</v>
+        <v>24.87564651929063</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1732593689997548</v>
+        <v>0.1727659732676876</v>
       </c>
       <c r="C18">
-        <v>16.15882908952094</v>
+        <v>16.05677367814893</v>
       </c>
       <c r="D18">
-        <v>18.95102908952094</v>
+        <v>19.02467367814893</v>
       </c>
       <c r="E18">
-        <v>0.7412000000000001</v>
+        <v>0.9169000000000005</v>
       </c>
       <c r="F18">
-        <v>2.8112</v>
+        <v>2.9869</v>
       </c>
       <c r="G18">
         <v>0.019</v>
@@ -2745,28 +2745,28 @@
         <v>3.5175</v>
       </c>
       <c r="M18">
-        <v>0.14140336</v>
+        <v>0.15024107</v>
       </c>
       <c r="N18">
-        <v>3.37609664</v>
+        <v>3.36725893</v>
       </c>
       <c r="O18">
-        <v>0.9790680255999998</v>
+        <v>0.9765050896999998</v>
       </c>
       <c r="P18">
-        <v>2.3970286144</v>
+        <v>2.3907538403</v>
       </c>
       <c r="Q18">
-        <v>2.9670286144</v>
+        <v>2.9607538403</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1994586773806605</v>
+        <v>0.2008370641779369</v>
       </c>
       <c r="T18">
-        <v>0.9397573427024778</v>
+        <v>0.9481873847665238</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>24.87564651929063</v>
+        <v>23.41237319462648</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1727659732676876</v>
+        <v>0.1722725775356204</v>
       </c>
       <c r="C19">
-        <v>16.05677367814893</v>
+        <v>15.95529287237801</v>
       </c>
       <c r="D19">
-        <v>19.02467367814893</v>
+        <v>19.09889287237802</v>
       </c>
       <c r="E19">
-        <v>0.9169000000000005</v>
+        <v>1.0926</v>
       </c>
       <c r="F19">
-        <v>2.9869</v>
+        <v>3.1626</v>
       </c>
       <c r="G19">
         <v>0.019</v>
@@ -2827,28 +2827,28 @@
         <v>3.5175</v>
       </c>
       <c r="M19">
-        <v>0.15024107</v>
+        <v>0.15907878</v>
       </c>
       <c r="N19">
-        <v>3.36725893</v>
+        <v>3.358421219999999</v>
       </c>
       <c r="O19">
-        <v>0.9765050896999998</v>
+        <v>0.9739421537999998</v>
       </c>
       <c r="P19">
-        <v>2.3907538403</v>
+        <v>2.384479066199999</v>
       </c>
       <c r="Q19">
-        <v>2.9607538403</v>
+        <v>2.954479066199999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2008370641779369</v>
+        <v>0.2022490701653907</v>
       </c>
       <c r="T19">
-        <v>0.9481873847665238</v>
+        <v>0.9568230376126196</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.41237319462648</v>
+        <v>22.111685794925</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1722725775356204</v>
+        <v>0.1717791818035532</v>
       </c>
       <c r="C20">
-        <v>15.95529287237801</v>
+        <v>15.854393423513</v>
       </c>
       <c r="D20">
-        <v>19.09889287237801</v>
+        <v>19.173693423513</v>
       </c>
       <c r="E20">
-        <v>1.0926</v>
+        <v>1.2683</v>
       </c>
       <c r="F20">
-        <v>3.1626</v>
+        <v>3.3383</v>
       </c>
       <c r="G20">
         <v>0.019</v>
@@ -2909,28 +2909,28 @@
         <v>3.5175</v>
       </c>
       <c r="M20">
-        <v>0.15907878</v>
+        <v>0.16791649</v>
       </c>
       <c r="N20">
-        <v>3.358421219999999</v>
+        <v>3.34958351</v>
       </c>
       <c r="O20">
-        <v>0.9739421537999998</v>
+        <v>0.9713792178999998</v>
       </c>
       <c r="P20">
-        <v>2.384479066199999</v>
+        <v>2.3782042921</v>
       </c>
       <c r="Q20">
-        <v>2.954479066199999</v>
+        <v>2.948204292099999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2022490701653907</v>
+        <v>0.2036959404982138</v>
       </c>
       <c r="T20">
-        <v>0.9568230376126196</v>
+        <v>0.9656719164549152</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.11168579492501</v>
+        <v>20.94791285835</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1717791818035532</v>
+        <v>0.171285786071486</v>
       </c>
       <c r="C21">
-        <v>15.854393423513</v>
+        <v>15.75408218904009</v>
       </c>
       <c r="D21">
-        <v>19.173693423513</v>
+        <v>19.24908218904009</v>
       </c>
       <c r="E21">
-        <v>1.2683</v>
+        <v>1.444</v>
       </c>
       <c r="F21">
-        <v>3.3383</v>
+        <v>3.514</v>
       </c>
       <c r="G21">
         <v>0.019</v>
@@ -2991,28 +2991,28 @@
         <v>3.5175</v>
       </c>
       <c r="M21">
-        <v>0.16791649</v>
+        <v>0.1767542</v>
       </c>
       <c r="N21">
-        <v>3.34958351</v>
+        <v>3.3407458</v>
       </c>
       <c r="O21">
-        <v>0.9713792178999998</v>
+        <v>0.9688162819999998</v>
       </c>
       <c r="P21">
-        <v>2.3782042921</v>
+        <v>2.371929518</v>
       </c>
       <c r="Q21">
-        <v>2.948204292099999</v>
+        <v>2.941929518</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2036959404982138</v>
+        <v>0.2051789825893575</v>
       </c>
       <c r="T21">
-        <v>0.9656719164549152</v>
+        <v>0.9747420172682685</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.94791285835</v>
+        <v>19.9005172154325</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.171285786071486</v>
+        <v>0.1707923903394188</v>
       </c>
       <c r="C22">
-        <v>15.75408218904009</v>
+        <v>15.65436613472265</v>
       </c>
       <c r="D22">
-        <v>19.24908218904009</v>
+        <v>19.32506613472265</v>
       </c>
       <c r="E22">
-        <v>1.444</v>
+        <v>1.6197</v>
       </c>
       <c r="F22">
-        <v>3.514</v>
+        <v>3.6897</v>
       </c>
       <c r="G22">
         <v>0.019</v>
@@ -3073,28 +3073,28 @@
         <v>3.5175</v>
       </c>
       <c r="M22">
-        <v>0.1767542</v>
+        <v>0.18559191</v>
       </c>
       <c r="N22">
-        <v>3.3407458</v>
+        <v>3.33190809</v>
       </c>
       <c r="O22">
-        <v>0.9688162819999998</v>
+        <v>0.9662533460999999</v>
       </c>
       <c r="P22">
-        <v>2.371929518</v>
+        <v>2.3656547439</v>
       </c>
       <c r="Q22">
-        <v>2.941929518</v>
+        <v>2.9356547439</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2051789825893575</v>
+        <v>0.2066995700498972</v>
       </c>
       <c r="T22">
-        <v>0.9747420172682685</v>
+        <v>0.9840417408870229</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.9005172154325</v>
+        <v>18.95287353850714</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1707923903394188</v>
+        <v>0.1702989946073516</v>
       </c>
       <c r="C23">
-        <v>15.65436613472265</v>
+        <v>15.55525233674669</v>
       </c>
       <c r="D23">
-        <v>19.32506613472265</v>
+        <v>19.40165233674669</v>
       </c>
       <c r="E23">
-        <v>1.6197</v>
+        <v>1.7954</v>
       </c>
       <c r="F23">
-        <v>3.6897</v>
+        <v>3.8654</v>
       </c>
       <c r="G23">
         <v>0.019</v>
@@ -3155,28 +3155,28 @@
         <v>3.5175</v>
       </c>
       <c r="M23">
-        <v>0.18559191</v>
+        <v>0.19442962</v>
       </c>
       <c r="N23">
-        <v>3.33190809</v>
+        <v>3.323070379999999</v>
       </c>
       <c r="O23">
-        <v>0.9662533460999999</v>
+        <v>0.9636904101999998</v>
       </c>
       <c r="P23">
-        <v>2.3656547439</v>
+        <v>2.3593799698</v>
       </c>
       <c r="Q23">
-        <v>2.9356547439</v>
+        <v>2.929379969799999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2066995700498972</v>
+        <v>0.208259146932502</v>
       </c>
       <c r="T23">
-        <v>0.9840417408870229</v>
+        <v>0.9935799189575403</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.95287353850715</v>
+        <v>18.09137928675682</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1702989946073516</v>
+        <v>0.1698055988752844</v>
       </c>
       <c r="C24">
-        <v>15.55525233674669</v>
+        <v>15.45674798391767</v>
       </c>
       <c r="D24">
-        <v>19.40165233674669</v>
+        <v>19.47884798391767</v>
       </c>
       <c r="E24">
-        <v>1.7954</v>
+        <v>1.9711</v>
       </c>
       <c r="F24">
-        <v>3.8654</v>
+        <v>4.0411</v>
       </c>
       <c r="G24">
         <v>0.019</v>
@@ -3237,28 +3237,28 @@
         <v>3.5175</v>
       </c>
       <c r="M24">
-        <v>0.19442962</v>
+        <v>0.20326733</v>
       </c>
       <c r="N24">
-        <v>3.323070379999999</v>
+        <v>3.31423267</v>
       </c>
       <c r="O24">
-        <v>0.9636904101999998</v>
+        <v>0.9611274742999998</v>
       </c>
       <c r="P24">
-        <v>2.3593799698</v>
+        <v>2.3531051957</v>
       </c>
       <c r="Q24">
-        <v>2.929379969799999</v>
+        <v>2.923105195699999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.208259146932502</v>
+        <v>0.2098592323055641</v>
       </c>
       <c r="T24">
-        <v>0.9935799189575403</v>
+        <v>1.003365841913006</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.09137928675682</v>
+        <v>17.30479757863696</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1698055988752844</v>
+        <v>0.1693122031432171</v>
       </c>
       <c r="C25">
-        <v>15.45674798391767</v>
+        <v>15.35886037990989</v>
       </c>
       <c r="D25">
-        <v>19.47884798391767</v>
+        <v>19.55666037990989</v>
       </c>
       <c r="E25">
-        <v>1.9711</v>
+        <v>2.1468</v>
       </c>
       <c r="F25">
-        <v>4.0411</v>
+        <v>4.2168</v>
       </c>
       <c r="G25">
         <v>0.019</v>
@@ -3319,28 +3319,28 @@
         <v>3.5175</v>
       </c>
       <c r="M25">
-        <v>0.20326733</v>
+        <v>0.21210504</v>
       </c>
       <c r="N25">
-        <v>3.31423267</v>
+        <v>3.30539496</v>
       </c>
       <c r="O25">
-        <v>0.9611274742999998</v>
+        <v>0.9585645383999999</v>
       </c>
       <c r="P25">
-        <v>2.3531051957</v>
+        <v>2.3468304216</v>
       </c>
       <c r="Q25">
-        <v>2.923105195699999</v>
+        <v>2.9168304216</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2098592323055641</v>
+        <v>0.2115014251884436</v>
       </c>
       <c r="T25">
-        <v>1.003365841913006</v>
+        <v>1.013409289156774</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.30479757863696</v>
+        <v>16.58376434619375</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1693122031432171</v>
+        <v>0.1688188074111499</v>
       </c>
       <c r="C26">
-        <v>15.35886037990989</v>
+        <v>15.26159694557002</v>
       </c>
       <c r="D26">
-        <v>19.55666037990989</v>
+        <v>19.63509694557002</v>
       </c>
       <c r="E26">
-        <v>2.1468</v>
+        <v>2.3225</v>
       </c>
       <c r="F26">
-        <v>4.2168</v>
+        <v>4.3925</v>
       </c>
       <c r="G26">
         <v>0.019</v>
@@ -3401,28 +3401,28 @@
         <v>3.5175</v>
       </c>
       <c r="M26">
-        <v>0.21210504</v>
+        <v>0.22094275</v>
       </c>
       <c r="N26">
-        <v>3.30539496</v>
+        <v>3.29655725</v>
       </c>
       <c r="O26">
-        <v>0.9585645383999999</v>
+        <v>0.9560016024999999</v>
       </c>
       <c r="P26">
-        <v>2.3468304216</v>
+        <v>2.3405556475</v>
       </c>
       <c r="Q26">
-        <v>2.9168304216</v>
+        <v>2.9105556475</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2115014251884436</v>
+        <v>0.2131874098815333</v>
       </c>
       <c r="T26">
-        <v>1.013409289156774</v>
+        <v>1.023720561660375</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.58376434619375</v>
+        <v>15.920413772346</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1688188074111499</v>
+        <v>0.1683254116790828</v>
       </c>
       <c r="C27">
-        <v>15.26159694557002</v>
+        <v>15.16496522127632</v>
       </c>
       <c r="D27">
-        <v>19.63509694557002</v>
+        <v>19.71416522127632</v>
       </c>
       <c r="E27">
-        <v>2.3225</v>
+        <v>2.4982</v>
       </c>
       <c r="F27">
-        <v>4.3925</v>
+        <v>4.5682</v>
       </c>
       <c r="G27">
         <v>0.019</v>
@@ -3483,28 +3483,28 @@
         <v>3.5175</v>
       </c>
       <c r="M27">
-        <v>0.22094275</v>
+        <v>0.22978046</v>
       </c>
       <c r="N27">
-        <v>3.29655725</v>
+        <v>3.287719539999999</v>
       </c>
       <c r="O27">
-        <v>0.9560016024999999</v>
+        <v>0.9534386665999998</v>
       </c>
       <c r="P27">
-        <v>2.3405556475</v>
+        <v>2.3342808734</v>
       </c>
       <c r="Q27">
-        <v>2.9105556475</v>
+        <v>2.904280873399999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2131874098815333</v>
+        <v>0.2149189617284902</v>
       </c>
       <c r="T27">
-        <v>1.023720561660375</v>
+        <v>1.034310517204615</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.920413772346</v>
+        <v>15.30809016571731</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1683254116790828</v>
+        <v>0.1678320159470155</v>
       </c>
       <c r="C28">
-        <v>15.16496522127632</v>
+        <v>15.06897286935508</v>
       </c>
       <c r="D28">
-        <v>19.71416522127632</v>
+        <v>19.79387286935508</v>
       </c>
       <c r="E28">
-        <v>2.4982</v>
+        <v>2.6739</v>
       </c>
       <c r="F28">
-        <v>4.5682</v>
+        <v>4.7439</v>
       </c>
       <c r="G28">
         <v>0.019</v>
@@ -3565,28 +3565,28 @@
         <v>3.5175</v>
       </c>
       <c r="M28">
-        <v>0.22978046</v>
+        <v>0.23861817</v>
       </c>
       <c r="N28">
-        <v>3.287719539999999</v>
+        <v>3.27888183</v>
       </c>
       <c r="O28">
-        <v>0.9534386665999998</v>
+        <v>0.9508757306999998</v>
       </c>
       <c r="P28">
-        <v>2.3342808734</v>
+        <v>2.3280060993</v>
       </c>
       <c r="Q28">
-        <v>2.904280873399999</v>
+        <v>2.898006099299999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2149189617284902</v>
+        <v>0.2166979533520761</v>
       </c>
       <c r="T28">
-        <v>1.034310517204615</v>
+        <v>1.045190608517189</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.30809016571731</v>
+        <v>14.74112386328333</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1678320159470155</v>
+        <v>0.1673386202149484</v>
       </c>
       <c r="C29">
-        <v>15.06897286935508</v>
+        <v>14.97362767655584</v>
       </c>
       <c r="D29">
-        <v>19.79387286935508</v>
+        <v>19.87422767655585</v>
       </c>
       <c r="E29">
-        <v>2.6739</v>
+        <v>2.849600000000001</v>
       </c>
       <c r="F29">
-        <v>4.7439</v>
+        <v>4.919600000000001</v>
       </c>
       <c r="G29">
         <v>0.019</v>
@@ -3647,28 +3647,28 @@
         <v>3.5175</v>
       </c>
       <c r="M29">
-        <v>0.23861817</v>
+        <v>0.24745588</v>
       </c>
       <c r="N29">
-        <v>3.27888183</v>
+        <v>3.27004412</v>
       </c>
       <c r="O29">
-        <v>0.9508757306999998</v>
+        <v>0.9483127947999999</v>
       </c>
       <c r="P29">
-        <v>2.3280060993</v>
+        <v>2.3217313252</v>
       </c>
       <c r="Q29">
-        <v>2.898006099299999</v>
+        <v>2.8917313252</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2166979533520761</v>
+        <v>0.2185263614096505</v>
       </c>
       <c r="T29">
-        <v>1.045190608517189</v>
+        <v>1.056372924588447</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.74112386328333</v>
+        <v>14.21465515388036</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1673386202149484</v>
+        <v>0.1668452244828811</v>
       </c>
       <c r="C30">
-        <v>14.97362767655584</v>
+        <v>14.87893755658735</v>
       </c>
       <c r="D30">
-        <v>19.87422767655585</v>
+        <v>19.95523755658736</v>
       </c>
       <c r="E30">
-        <v>2.849600000000001</v>
+        <v>3.025300000000001</v>
       </c>
       <c r="F30">
-        <v>4.919600000000001</v>
+        <v>5.095300000000001</v>
       </c>
       <c r="G30">
         <v>0.019</v>
@@ -3729,28 +3729,28 @@
         <v>3.5175</v>
       </c>
       <c r="M30">
-        <v>0.24745588</v>
+        <v>0.25629359</v>
       </c>
       <c r="N30">
-        <v>3.27004412</v>
+        <v>3.26120641</v>
       </c>
       <c r="O30">
-        <v>0.9483127947999999</v>
+        <v>0.9457498588999999</v>
       </c>
       <c r="P30">
-        <v>2.3217313252</v>
+        <v>2.3154565511</v>
       </c>
       <c r="Q30">
-        <v>2.8917313252</v>
+        <v>2.8854565511</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2185263614096505</v>
+        <v>0.2204062739195509</v>
       </c>
       <c r="T30">
-        <v>1.056372924588447</v>
+        <v>1.067870235478613</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.21465515388036</v>
+        <v>13.72449463133276</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1668452244828811</v>
+        <v>0.1663518287508139</v>
       </c>
       <c r="C31">
-        <v>14.87893755658735</v>
+        <v>14.78491055271552</v>
       </c>
       <c r="D31">
-        <v>19.95523755658736</v>
+        <v>20.03691055271552</v>
       </c>
       <c r="E31">
-        <v>3.0253</v>
+        <v>3.201</v>
       </c>
       <c r="F31">
-        <v>5.0953</v>
+        <v>5.271</v>
       </c>
       <c r="G31">
         <v>0.019</v>
@@ -3811,28 +3811,28 @@
         <v>3.5175</v>
       </c>
       <c r="M31">
-        <v>0.25629359</v>
+        <v>0.2651313</v>
       </c>
       <c r="N31">
-        <v>3.26120641</v>
+        <v>3.2523687</v>
       </c>
       <c r="O31">
-        <v>0.9457498588999999</v>
+        <v>0.943186923</v>
       </c>
       <c r="P31">
-        <v>2.3154565511</v>
+        <v>2.309181777</v>
       </c>
       <c r="Q31">
-        <v>2.8854565511</v>
+        <v>2.879181777</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2204062739195509</v>
+        <v>0.2223398982154484</v>
       </c>
       <c r="T31">
-        <v>1.067870235478613</v>
+        <v>1.07969604096564</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.72449463133276</v>
+        <v>13.26701147695501</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1663518287508139</v>
+        <v>0.1661885830187467</v>
       </c>
       <c r="C32">
-        <v>14.78491055271552</v>
+        <v>14.63638040594847</v>
       </c>
       <c r="D32">
-        <v>20.03691055271552</v>
+        <v>20.06408040594847</v>
       </c>
       <c r="E32">
-        <v>3.201</v>
+        <v>3.3767</v>
       </c>
       <c r="F32">
-        <v>5.271</v>
+        <v>5.4467</v>
       </c>
       <c r="G32">
         <v>0.019</v>
@@ -3893,45 +3893,45 @@
         <v>3.5175</v>
       </c>
       <c r="M32">
-        <v>0.2651313</v>
+        <v>0.28213906</v>
       </c>
       <c r="N32">
-        <v>3.2523687</v>
+        <v>3.23536094</v>
       </c>
       <c r="O32">
-        <v>0.943186923</v>
+        <v>0.9382546725999998</v>
       </c>
       <c r="P32">
-        <v>2.309181777</v>
+        <v>2.2971062674</v>
       </c>
       <c r="Q32">
-        <v>2.879181777</v>
+        <v>2.8671062674</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2223398982154484</v>
+        <v>0.2243295695923865</v>
       </c>
       <c r="T32">
-        <v>1.07969604096564</v>
+        <v>1.091864623423307</v>
       </c>
       <c r="U32">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V32">
         <v>0.29</v>
       </c>
       <c r="W32">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y32">
-        <v>13.26701147695501</v>
+        <v>12.46725639477214</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1661885830187467</v>
+        <v>0.1657058372866795</v>
       </c>
       <c r="C33">
-        <v>14.63638040594847</v>
+        <v>14.54145920206886</v>
       </c>
       <c r="D33">
-        <v>20.06408040594847</v>
+        <v>20.14485920206886</v>
       </c>
       <c r="E33">
-        <v>3.3767</v>
+        <v>3.5524</v>
       </c>
       <c r="F33">
-        <v>5.4467</v>
+        <v>5.6224</v>
       </c>
       <c r="G33">
         <v>0.019</v>
@@ -3975,28 +3975,28 @@
         <v>3.5175</v>
       </c>
       <c r="M33">
-        <v>0.28213906</v>
+        <v>0.29124032</v>
       </c>
       <c r="N33">
-        <v>3.23536094</v>
+        <v>3.22625968</v>
       </c>
       <c r="O33">
-        <v>0.9382546725999998</v>
+        <v>0.9356153071999999</v>
       </c>
       <c r="P33">
-        <v>2.2971062674</v>
+        <v>2.2906443728</v>
       </c>
       <c r="Q33">
-        <v>2.8671062674</v>
+        <v>2.8606443728</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2243295695923865</v>
+        <v>0.2263777607157051</v>
       </c>
       <c r="T33">
-        <v>1.091864623423307</v>
+        <v>1.104391105365022</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>12.46725639477214</v>
+        <v>12.07765463243551</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1657058372866795</v>
+        <v>0.1652230915546123</v>
       </c>
       <c r="C34">
-        <v>14.54145920206886</v>
+        <v>14.4471910648376</v>
       </c>
       <c r="D34">
-        <v>20.14485920206886</v>
+        <v>20.2262910648376</v>
       </c>
       <c r="E34">
-        <v>3.5524</v>
+        <v>3.728100000000001</v>
       </c>
       <c r="F34">
-        <v>5.6224</v>
+        <v>5.798100000000001</v>
       </c>
       <c r="G34">
         <v>0.019</v>
@@ -4057,28 +4057,28 @@
         <v>3.5175</v>
       </c>
       <c r="M34">
-        <v>0.29124032</v>
+        <v>0.3003415800000001</v>
       </c>
       <c r="N34">
-        <v>3.22625968</v>
+        <v>3.21715842</v>
       </c>
       <c r="O34">
-        <v>0.9356153071999999</v>
+        <v>0.9329759417999999</v>
       </c>
       <c r="P34">
-        <v>2.2906443728</v>
+        <v>2.2841824782</v>
       </c>
       <c r="Q34">
-        <v>2.8606443728</v>
+        <v>2.8541824782</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2263777607157051</v>
+        <v>0.2284870918725556</v>
       </c>
       <c r="T34">
-        <v>1.104391105365022</v>
+        <v>1.117291512140818</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.07765463243551</v>
+        <v>11.71166509811928</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1652230915546123</v>
+        <v>0.1647403458225451</v>
       </c>
       <c r="C35">
-        <v>14.4471910648376</v>
+        <v>14.35358394610151</v>
       </c>
       <c r="D35">
-        <v>20.2262910648376</v>
+        <v>20.30838394610151</v>
       </c>
       <c r="E35">
-        <v>3.728100000000001</v>
+        <v>3.903800000000001</v>
       </c>
       <c r="F35">
-        <v>5.798100000000001</v>
+        <v>5.973800000000001</v>
       </c>
       <c r="G35">
         <v>0.019</v>
@@ -4139,28 +4139,28 @@
         <v>3.5175</v>
       </c>
       <c r="M35">
-        <v>0.3003415800000001</v>
+        <v>0.3094428400000001</v>
       </c>
       <c r="N35">
-        <v>3.21715842</v>
+        <v>3.20805716</v>
       </c>
       <c r="O35">
-        <v>0.9329759417999999</v>
+        <v>0.9303365763999998</v>
       </c>
       <c r="P35">
-        <v>2.2841824782</v>
+        <v>2.2777205836</v>
       </c>
       <c r="Q35">
-        <v>2.8541824782</v>
+        <v>2.8477205836</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2284870918725556</v>
+        <v>0.2306603421553713</v>
       </c>
       <c r="T35">
-        <v>1.117291512140818</v>
+        <v>1.130582840334063</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.71166509811928</v>
+        <v>11.3672043599393</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1647403458225451</v>
+        <v>0.1642576000904779</v>
       </c>
       <c r="C36">
-        <v>14.35358394610151</v>
+        <v>14.26064592733087</v>
       </c>
       <c r="D36">
-        <v>20.30838394610151</v>
+        <v>20.39114592733088</v>
       </c>
       <c r="E36">
-        <v>3.903800000000001</v>
+        <v>4.079500000000001</v>
       </c>
       <c r="F36">
-        <v>5.973800000000001</v>
+        <v>6.149500000000001</v>
       </c>
       <c r="G36">
         <v>0.019</v>
@@ -4221,28 +4221,28 @@
         <v>3.5175</v>
       </c>
       <c r="M36">
-        <v>0.3094428400000001</v>
+        <v>0.3185441000000001</v>
       </c>
       <c r="N36">
-        <v>3.20805716</v>
+        <v>3.1989559</v>
       </c>
       <c r="O36">
-        <v>0.9303365763999998</v>
+        <v>0.9276972109999998</v>
       </c>
       <c r="P36">
-        <v>2.2777205836</v>
+        <v>2.271258689</v>
       </c>
       <c r="Q36">
-        <v>2.8477205836</v>
+        <v>2.841258689</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2306603421553713</v>
+        <v>0.2329004616776583</v>
       </c>
       <c r="T36">
-        <v>1.130582840334063</v>
+        <v>1.144283132471716</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.3672043599393</v>
+        <v>11.04242709251246</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1642576000904779</v>
+        <v>0.1637748543584107</v>
       </c>
       <c r="C37">
-        <v>14.26064592733087</v>
+        <v>14.16838522227141</v>
       </c>
       <c r="D37">
-        <v>20.39114592733088</v>
+        <v>20.47458522227141</v>
       </c>
       <c r="E37">
-        <v>4.079500000000001</v>
+        <v>4.2552</v>
       </c>
       <c r="F37">
-        <v>6.149500000000001</v>
+        <v>6.325200000000001</v>
       </c>
       <c r="G37">
         <v>0.019</v>
@@ -4303,28 +4303,28 @@
         <v>3.5175</v>
       </c>
       <c r="M37">
-        <v>0.3185441000000001</v>
+        <v>0.32764536</v>
       </c>
       <c r="N37">
-        <v>3.1989559</v>
+        <v>3.18985464</v>
       </c>
       <c r="O37">
-        <v>0.9276972109999998</v>
+        <v>0.9250578455999998</v>
       </c>
       <c r="P37">
-        <v>2.271258689</v>
+        <v>2.2647967944</v>
       </c>
       <c r="Q37">
-        <v>2.841258689</v>
+        <v>2.834796794399999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2329004616776583</v>
+        <v>0.2352105849350167</v>
       </c>
       <c r="T37">
-        <v>1.144283132471716</v>
+        <v>1.158411558738669</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.04242709251246</v>
+        <v>10.73569300660934</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1637748543584107</v>
+        <v>0.1632921086263435</v>
       </c>
       <c r="C38">
-        <v>14.16838522227141</v>
+        <v>14.07681017966179</v>
       </c>
       <c r="D38">
-        <v>20.47458522227141</v>
+        <v>20.55871017966179</v>
       </c>
       <c r="E38">
-        <v>4.2552</v>
+        <v>4.430899999999999</v>
       </c>
       <c r="F38">
-        <v>6.3252</v>
+        <v>6.5009</v>
       </c>
       <c r="G38">
         <v>0.019</v>
@@ -4385,28 +4385,28 @@
         <v>3.5175</v>
       </c>
       <c r="M38">
-        <v>0.32764536</v>
+        <v>0.33674662</v>
       </c>
       <c r="N38">
-        <v>3.18985464</v>
+        <v>3.18075338</v>
       </c>
       <c r="O38">
-        <v>0.9250578455999998</v>
+        <v>0.9224184801999998</v>
       </c>
       <c r="P38">
-        <v>2.2647967944</v>
+        <v>2.2583348998</v>
       </c>
       <c r="Q38">
-        <v>2.834796794399999</v>
+        <v>2.8283348998</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2352105849350167</v>
+        <v>0.2375940454386404</v>
       </c>
       <c r="T38">
-        <v>1.158411558738669</v>
+        <v>1.172988506474415</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.73569300660934</v>
+        <v>10.44553914156585</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1632921086263435</v>
+        <v>0.1628093628942762</v>
       </c>
       <c r="C39">
-        <v>14.07681017966179</v>
+        <v>13.98592928601832</v>
       </c>
       <c r="D39">
-        <v>20.55871017966179</v>
+        <v>20.64352928601832</v>
       </c>
       <c r="E39">
-        <v>4.430899999999999</v>
+        <v>4.6066</v>
       </c>
       <c r="F39">
-        <v>6.5009</v>
+        <v>6.676600000000001</v>
       </c>
       <c r="G39">
         <v>0.019</v>
@@ -4467,28 +4467,28 @@
         <v>3.5175</v>
       </c>
       <c r="M39">
-        <v>0.33674662</v>
+        <v>0.34584788</v>
       </c>
       <c r="N39">
-        <v>3.18075338</v>
+        <v>3.17165212</v>
       </c>
       <c r="O39">
-        <v>0.9224184801999998</v>
+        <v>0.9197791147999999</v>
       </c>
       <c r="P39">
-        <v>2.2583348998</v>
+        <v>2.2518730052</v>
       </c>
       <c r="Q39">
-        <v>2.8283348998</v>
+        <v>2.8218730052</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2375940454386404</v>
+        <v>0.2400543917649617</v>
       </c>
       <c r="T39">
-        <v>1.172988506474415</v>
+        <v>1.188035678330669</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.44553914156585</v>
+        <v>10.17065653257727</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1628093628942762</v>
+        <v>0.162326617162209</v>
       </c>
       <c r="C40">
-        <v>13.98592928601832</v>
+        <v>13.8957511684888</v>
       </c>
       <c r="D40">
-        <v>20.64352928601832</v>
+        <v>20.72905116848881</v>
       </c>
       <c r="E40">
-        <v>4.6066</v>
+        <v>4.782300000000001</v>
       </c>
       <c r="F40">
-        <v>6.676600000000001</v>
+        <v>6.852300000000001</v>
       </c>
       <c r="G40">
         <v>0.019</v>
@@ -4549,28 +4549,28 @@
         <v>3.5175</v>
       </c>
       <c r="M40">
-        <v>0.34584788</v>
+        <v>0.35494914</v>
       </c>
       <c r="N40">
-        <v>3.17165212</v>
+        <v>3.16255086</v>
       </c>
       <c r="O40">
-        <v>0.9197791147999999</v>
+        <v>0.9171397493999999</v>
       </c>
       <c r="P40">
-        <v>2.2518730052</v>
+        <v>2.2454111106</v>
       </c>
       <c r="Q40">
-        <v>2.8218730052</v>
+        <v>2.815411110599999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2400543917649617</v>
+        <v>0.2425954051839492</v>
       </c>
       <c r="T40">
-        <v>1.188035678330669</v>
+        <v>1.20357620008385</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.17065653257727</v>
+        <v>9.909870467639392</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.162326617162209</v>
+        <v>0.1623266714301418</v>
       </c>
       <c r="C41">
-        <v>13.8957511684888</v>
+        <v>13.72004151470961</v>
       </c>
       <c r="D41">
-        <v>20.72905116848881</v>
+        <v>20.72904151470961</v>
       </c>
       <c r="E41">
-        <v>4.782300000000001</v>
+        <v>4.958</v>
       </c>
       <c r="F41">
-        <v>6.852300000000001</v>
+        <v>7.028</v>
       </c>
       <c r="G41">
         <v>0.019</v>
@@ -4631,45 +4631,45 @@
         <v>3.5175</v>
       </c>
       <c r="M41">
-        <v>0.35494914</v>
+        <v>0.375998</v>
       </c>
       <c r="N41">
-        <v>3.16255086</v>
+        <v>3.141502</v>
       </c>
       <c r="O41">
-        <v>0.9171397493999999</v>
+        <v>0.9110355799999998</v>
       </c>
       <c r="P41">
-        <v>2.2454111106</v>
+        <v>2.23046642</v>
       </c>
       <c r="Q41">
-        <v>2.815411110599999</v>
+        <v>2.80046642</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2425954051839492</v>
+        <v>0.2452211190502364</v>
       </c>
       <c r="T41">
-        <v>1.20357620008385</v>
+        <v>1.219634739228803</v>
       </c>
       <c r="U41">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V41">
         <v>0.29</v>
       </c>
       <c r="W41">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>9.909870467639392</v>
+        <v>9.35510295267528</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1623266714301418</v>
+        <v>0.1618559956980746</v>
       </c>
       <c r="C42">
-        <v>13.72004151470961</v>
+        <v>13.62841004327896</v>
       </c>
       <c r="D42">
-        <v>20.72904151470961</v>
+        <v>20.81311004327896</v>
       </c>
       <c r="E42">
-        <v>4.958</v>
+        <v>5.133700000000001</v>
       </c>
       <c r="F42">
-        <v>7.028</v>
+        <v>7.2037</v>
       </c>
       <c r="G42">
         <v>0.019</v>
@@ -4713,28 +4713,28 @@
         <v>3.5175</v>
       </c>
       <c r="M42">
-        <v>0.375998</v>
+        <v>0.38539795</v>
       </c>
       <c r="N42">
-        <v>3.141502</v>
+        <v>3.132102049999999</v>
       </c>
       <c r="O42">
-        <v>0.9110355799999998</v>
+        <v>0.9083095944999998</v>
       </c>
       <c r="P42">
-        <v>2.23046642</v>
+        <v>2.223792455499999</v>
       </c>
       <c r="Q42">
-        <v>2.80046642</v>
+        <v>2.793792455499999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2452211190502364</v>
+        <v>0.2479358401662282</v>
       </c>
       <c r="T42">
-        <v>1.219634739228803</v>
+        <v>1.236237635632907</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.35510295267528</v>
+        <v>9.126929709927101</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1618559956980746</v>
+        <v>0.1613853199660074</v>
       </c>
       <c r="C43">
-        <v>13.62841004327896</v>
+        <v>13.53746324385059</v>
       </c>
       <c r="D43">
-        <v>20.81311004327896</v>
+        <v>20.89786324385059</v>
       </c>
       <c r="E43">
-        <v>5.133700000000001</v>
+        <v>5.3094</v>
       </c>
       <c r="F43">
-        <v>7.2037</v>
+        <v>7.3794</v>
       </c>
       <c r="G43">
         <v>0.019</v>
@@ -4795,28 +4795,28 @@
         <v>3.5175</v>
       </c>
       <c r="M43">
-        <v>0.38539795</v>
+        <v>0.3947979</v>
       </c>
       <c r="N43">
-        <v>3.132102049999999</v>
+        <v>3.1227021</v>
       </c>
       <c r="O43">
-        <v>0.9083095944999998</v>
+        <v>0.9055836089999999</v>
       </c>
       <c r="P43">
-        <v>2.223792455499999</v>
+        <v>2.217118491</v>
       </c>
       <c r="Q43">
-        <v>2.793792455499999</v>
+        <v>2.787118491</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2479358401662282</v>
+        <v>0.2507441723551852</v>
       </c>
       <c r="T43">
-        <v>1.236237635632907</v>
+        <v>1.253413045706118</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.126929709927101</v>
+        <v>8.909621859690741</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1613853199660074</v>
+        <v>0.1609146442339402</v>
       </c>
       <c r="C44">
-        <v>13.53746324385059</v>
+        <v>13.4472095147955</v>
       </c>
       <c r="D44">
-        <v>20.89786324385059</v>
+        <v>20.9833095147955</v>
       </c>
       <c r="E44">
-        <v>5.3094</v>
+        <v>5.485100000000001</v>
       </c>
       <c r="F44">
-        <v>7.3794</v>
+        <v>7.5551</v>
       </c>
       <c r="G44">
         <v>0.019</v>
@@ -4877,28 +4877,28 @@
         <v>3.5175</v>
       </c>
       <c r="M44">
-        <v>0.3947979</v>
+        <v>0.40419785</v>
       </c>
       <c r="N44">
-        <v>3.1227021</v>
+        <v>3.11330215</v>
       </c>
       <c r="O44">
-        <v>0.9055836089999999</v>
+        <v>0.9028576234999998</v>
       </c>
       <c r="P44">
-        <v>2.217118491</v>
+        <v>2.2104445265</v>
       </c>
       <c r="Q44">
-        <v>2.787118491</v>
+        <v>2.7804445265</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2507441723551852</v>
+        <v>0.2536510425156845</v>
       </c>
       <c r="T44">
-        <v>1.253413045706118</v>
+        <v>1.27119110174681</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.909621859690743</v>
+        <v>8.702421351325841</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1609146442339402</v>
+        <v>0.160443968501873</v>
       </c>
       <c r="C45">
-        <v>13.4472095147955</v>
+        <v>13.35765739240415</v>
       </c>
       <c r="D45">
-        <v>20.9833095147955</v>
+        <v>21.06945739240415</v>
       </c>
       <c r="E45">
-        <v>5.485100000000001</v>
+        <v>5.6608</v>
       </c>
       <c r="F45">
-        <v>7.5551</v>
+        <v>7.7308</v>
       </c>
       <c r="G45">
         <v>0.019</v>
@@ -4959,28 +4959,28 @@
         <v>3.5175</v>
       </c>
       <c r="M45">
-        <v>0.40419785</v>
+        <v>0.4135978</v>
       </c>
       <c r="N45">
-        <v>3.11330215</v>
+        <v>3.103902199999999</v>
       </c>
       <c r="O45">
-        <v>0.9028576234999998</v>
+        <v>0.9001316379999997</v>
       </c>
       <c r="P45">
-        <v>2.2104445265</v>
+        <v>2.203770562</v>
       </c>
       <c r="Q45">
-        <v>2.7804445265</v>
+        <v>2.773770562</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2536510425156845</v>
+        <v>0.2566617294676303</v>
       </c>
       <c r="T45">
-        <v>1.27119110174681</v>
+        <v>1.289604088360384</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.702421351325841</v>
+        <v>8.504639047886617</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.160443968501873</v>
+        <v>0.1599732927698058</v>
       </c>
       <c r="C46">
-        <v>13.35765739240415</v>
+        <v>13.26881555372934</v>
       </c>
       <c r="D46">
-        <v>21.06945739240415</v>
+        <v>21.15631555372935</v>
       </c>
       <c r="E46">
-        <v>5.6608</v>
+        <v>5.836500000000001</v>
       </c>
       <c r="F46">
-        <v>7.7308</v>
+        <v>7.9065</v>
       </c>
       <c r="G46">
         <v>0.019</v>
@@ -5041,28 +5041,28 @@
         <v>3.5175</v>
       </c>
       <c r="M46">
-        <v>0.4135978</v>
+        <v>0.42299775</v>
       </c>
       <c r="N46">
-        <v>3.103902199999999</v>
+        <v>3.09450225</v>
       </c>
       <c r="O46">
-        <v>0.9001316379999997</v>
+        <v>0.8974056524999998</v>
       </c>
       <c r="P46">
-        <v>2.203770562</v>
+        <v>2.1970965975</v>
       </c>
       <c r="Q46">
-        <v>2.773770562</v>
+        <v>2.7670965975</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2566617294676303</v>
+        <v>0.2597818959451014</v>
       </c>
       <c r="T46">
-        <v>1.289604088360384</v>
+        <v>1.308686638123543</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.504639047886617</v>
+        <v>8.315647069044694</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1599732927698058</v>
+        <v>0.1595026170377386</v>
       </c>
       <c r="C47">
-        <v>13.26881555372934</v>
+        <v>13.18069281949968</v>
       </c>
       <c r="D47">
-        <v>21.15631555372935</v>
+        <v>21.24389281949968</v>
       </c>
       <c r="E47">
-        <v>5.836500000000001</v>
+        <v>6.0122</v>
       </c>
       <c r="F47">
-        <v>7.9065</v>
+        <v>8.0822</v>
       </c>
       <c r="G47">
         <v>0.019</v>
@@ -5123,28 +5123,28 @@
         <v>3.5175</v>
       </c>
       <c r="M47">
-        <v>0.42299775</v>
+        <v>0.4323977</v>
       </c>
       <c r="N47">
-        <v>3.09450225</v>
+        <v>3.0851023</v>
       </c>
       <c r="O47">
-        <v>0.8974056524999998</v>
+        <v>0.8946796669999998</v>
       </c>
       <c r="P47">
-        <v>2.1970965975</v>
+        <v>2.190422633</v>
       </c>
       <c r="Q47">
-        <v>2.7670965975</v>
+        <v>2.760422633</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2597818959451014</v>
+        <v>0.2630176241439603</v>
       </c>
       <c r="T47">
-        <v>1.308686638123543</v>
+        <v>1.328475948989041</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.315647069044694</v>
+        <v>8.134872132761112</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1595026170377386</v>
+        <v>0.1590319413056714</v>
       </c>
       <c r="C48">
-        <v>13.18069281949968</v>
+        <v>13.09329815710563</v>
       </c>
       <c r="D48">
-        <v>21.24389281949968</v>
+        <v>21.33219815710564</v>
       </c>
       <c r="E48">
-        <v>6.0122</v>
+        <v>6.187900000000001</v>
       </c>
       <c r="F48">
-        <v>8.0822</v>
+        <v>8.257900000000001</v>
       </c>
       <c r="G48">
         <v>0.019</v>
@@ -5205,28 +5205,28 @@
         <v>3.5175</v>
       </c>
       <c r="M48">
-        <v>0.4323977</v>
+        <v>0.44179765</v>
       </c>
       <c r="N48">
-        <v>3.0851023</v>
+        <v>3.075702349999999</v>
       </c>
       <c r="O48">
-        <v>0.8946796669999998</v>
+        <v>0.8919536814999998</v>
       </c>
       <c r="P48">
-        <v>2.190422633</v>
+        <v>2.1837486685</v>
       </c>
       <c r="Q48">
-        <v>2.760422633</v>
+        <v>2.7537486685</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2630176241439603</v>
+        <v>0.2663754552937196</v>
       </c>
       <c r="T48">
-        <v>1.328475948989041</v>
+        <v>1.349012026302293</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.134872132761112</v>
+        <v>7.961789746957683</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1590319413056714</v>
+        <v>0.1585612655736042</v>
       </c>
       <c r="C49">
-        <v>13.09329815710563</v>
+        <v>13.00664068366051</v>
       </c>
       <c r="D49">
-        <v>21.33219815710564</v>
+        <v>21.42124068366051</v>
       </c>
       <c r="E49">
-        <v>6.187900000000001</v>
+        <v>6.3636</v>
       </c>
       <c r="F49">
-        <v>8.257900000000001</v>
+        <v>8.4336</v>
       </c>
       <c r="G49">
         <v>0.019</v>
@@ -5287,28 +5287,28 @@
         <v>3.5175</v>
       </c>
       <c r="M49">
-        <v>0.44179765</v>
+        <v>0.4511976</v>
       </c>
       <c r="N49">
-        <v>3.075702349999999</v>
+        <v>3.0663024</v>
       </c>
       <c r="O49">
-        <v>0.8919536814999998</v>
+        <v>0.8892276959999998</v>
       </c>
       <c r="P49">
-        <v>2.1837486685</v>
+        <v>2.177074704</v>
       </c>
       <c r="Q49">
-        <v>2.7537486685</v>
+        <v>2.747074704</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2663754552937196</v>
+        <v>0.2698624337953927</v>
       </c>
       <c r="T49">
-        <v>1.349012026302293</v>
+        <v>1.370337952742978</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.961789746957683</v>
+        <v>7.7959191272294</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1585612655736042</v>
+        <v>0.158090589841537</v>
       </c>
       <c r="C50">
-        <v>13.00664068366051</v>
+        <v>12.92072966913826</v>
       </c>
       <c r="D50">
-        <v>21.42124068366051</v>
+        <v>21.51102966913826</v>
       </c>
       <c r="E50">
-        <v>6.3636</v>
+        <v>6.539299999999999</v>
       </c>
       <c r="F50">
-        <v>8.4336</v>
+        <v>8.609299999999999</v>
       </c>
       <c r="G50">
         <v>0.019</v>
@@ -5369,28 +5369,28 @@
         <v>3.5175</v>
       </c>
       <c r="M50">
-        <v>0.4511976</v>
+        <v>0.46059755</v>
       </c>
       <c r="N50">
-        <v>3.0663024</v>
+        <v>3.056902449999999</v>
       </c>
       <c r="O50">
-        <v>0.8892276959999998</v>
+        <v>0.8865017104999998</v>
       </c>
       <c r="P50">
-        <v>2.177074704</v>
+        <v>2.1704007395</v>
       </c>
       <c r="Q50">
-        <v>2.747074704</v>
+        <v>2.7404007395</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2698624337953927</v>
+        <v>0.2734861565520332</v>
       </c>
       <c r="T50">
-        <v>1.370337952742978</v>
+        <v>1.392500190024474</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.7959191272294</v>
+        <v>7.636818736877779</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.158090589841537</v>
+        <v>0.1579039141094697</v>
       </c>
       <c r="C51">
-        <v>12.92072966913826</v>
+        <v>12.78084989221347</v>
       </c>
       <c r="D51">
-        <v>21.51102966913826</v>
+        <v>21.54684989221347</v>
       </c>
       <c r="E51">
-        <v>6.539299999999999</v>
+        <v>6.715</v>
       </c>
       <c r="F51">
-        <v>8.609299999999999</v>
+        <v>8.785</v>
       </c>
       <c r="G51">
         <v>0.019</v>
@@ -5451,45 +5451,45 @@
         <v>3.5175</v>
       </c>
       <c r="M51">
-        <v>0.46059755</v>
+        <v>0.4770255</v>
       </c>
       <c r="N51">
-        <v>3.056902449999999</v>
+        <v>3.0404745</v>
       </c>
       <c r="O51">
-        <v>0.8865017104999998</v>
+        <v>0.8817376049999999</v>
       </c>
       <c r="P51">
-        <v>2.1704007395</v>
+        <v>2.158736895</v>
       </c>
       <c r="Q51">
-        <v>2.7404007395</v>
+        <v>2.728736894999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2734861565520332</v>
+        <v>0.2772548282189395</v>
       </c>
       <c r="T51">
-        <v>1.392500190024474</v>
+        <v>1.415548916797231</v>
       </c>
       <c r="U51">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V51">
         <v>0.29</v>
       </c>
       <c r="W51">
-        <v>0.037985</v>
+        <v>0.038553</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y51">
-        <v>7.636818736877779</v>
+        <v>7.373819638572781</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1579039141094697</v>
+        <v>0.1574389183774025</v>
       </c>
       <c r="C52">
-        <v>12.78084989221347</v>
+        <v>12.69489631205518</v>
       </c>
       <c r="D52">
-        <v>21.54684989221347</v>
+        <v>21.63659631205518</v>
       </c>
       <c r="E52">
-        <v>6.715</v>
+        <v>6.890700000000001</v>
       </c>
       <c r="F52">
-        <v>8.785</v>
+        <v>8.960700000000001</v>
       </c>
       <c r="G52">
         <v>0.019</v>
@@ -5533,28 +5533,28 @@
         <v>3.5175</v>
       </c>
       <c r="M52">
-        <v>0.4770255</v>
+        <v>0.48656601</v>
       </c>
       <c r="N52">
-        <v>3.0404745</v>
+        <v>3.030933989999999</v>
       </c>
       <c r="O52">
-        <v>0.8817376049999999</v>
+        <v>0.8789708570999998</v>
       </c>
       <c r="P52">
-        <v>2.158736895</v>
+        <v>2.1519631329</v>
       </c>
       <c r="Q52">
-        <v>2.728736894999999</v>
+        <v>2.7219631329</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2772548282189395</v>
+        <v>0.2811773232191889</v>
       </c>
       <c r="T52">
-        <v>1.415548916797231</v>
+        <v>1.439538407928059</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.373819638572781</v>
+        <v>7.229234939777234</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1574389183774025</v>
+        <v>0.1569739226453353</v>
       </c>
       <c r="C53">
-        <v>12.69489631205518</v>
+        <v>12.60969347813668</v>
       </c>
       <c r="D53">
-        <v>21.63659631205518</v>
+        <v>21.72709347813668</v>
       </c>
       <c r="E53">
-        <v>6.890700000000001</v>
+        <v>7.0664</v>
       </c>
       <c r="F53">
-        <v>8.960700000000001</v>
+        <v>9.1364</v>
       </c>
       <c r="G53">
         <v>0.019</v>
@@ -5615,28 +5615,28 @@
         <v>3.5175</v>
       </c>
       <c r="M53">
-        <v>0.48656601</v>
+        <v>0.49610652</v>
       </c>
       <c r="N53">
-        <v>3.030933989999999</v>
+        <v>3.02139348</v>
       </c>
       <c r="O53">
-        <v>0.8789708570999998</v>
+        <v>0.8762041091999998</v>
       </c>
       <c r="P53">
-        <v>2.1519631329</v>
+        <v>2.1451893708</v>
       </c>
       <c r="Q53">
-        <v>2.7219631329</v>
+        <v>2.7151893708</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2811773232191889</v>
+        <v>0.2852632555111153</v>
       </c>
       <c r="T53">
-        <v>1.439538407928059</v>
+        <v>1.464527461189338</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.229234939777234</v>
+        <v>7.090211190935365</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1569739226453353</v>
+        <v>0.1565089269132681</v>
       </c>
       <c r="C54">
-        <v>12.60969347813668</v>
+        <v>12.52525085023164</v>
       </c>
       <c r="D54">
-        <v>21.72709347813668</v>
+        <v>21.81835085023165</v>
       </c>
       <c r="E54">
-        <v>7.0664</v>
+        <v>7.242100000000001</v>
       </c>
       <c r="F54">
-        <v>9.1364</v>
+        <v>9.312100000000001</v>
       </c>
       <c r="G54">
         <v>0.019</v>
@@ -5697,28 +5697,28 @@
         <v>3.5175</v>
       </c>
       <c r="M54">
-        <v>0.49610652</v>
+        <v>0.5056470300000001</v>
       </c>
       <c r="N54">
-        <v>3.02139348</v>
+        <v>3.01185297</v>
       </c>
       <c r="O54">
-        <v>0.8762041091999998</v>
+        <v>0.8734373612999998</v>
       </c>
       <c r="P54">
-        <v>2.1451893708</v>
+        <v>2.1384156087</v>
       </c>
       <c r="Q54">
-        <v>2.7151893708</v>
+        <v>2.7084156087</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2852632555111153</v>
+        <v>0.2895230572622726</v>
       </c>
       <c r="T54">
-        <v>1.464527461189338</v>
+        <v>1.490579878419182</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.090211190935365</v>
+        <v>6.956433621295074</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1565089269132681</v>
+        <v>0.1560439311812009</v>
       </c>
       <c r="C55">
-        <v>12.52525085023164</v>
+        <v>12.44157804771453</v>
       </c>
       <c r="D55">
-        <v>21.81835085023165</v>
+        <v>21.91037804771453</v>
       </c>
       <c r="E55">
-        <v>7.242100000000001</v>
+        <v>7.4178</v>
       </c>
       <c r="F55">
-        <v>9.312100000000001</v>
+        <v>9.4878</v>
       </c>
       <c r="G55">
         <v>0.019</v>
@@ -5779,28 +5779,28 @@
         <v>3.5175</v>
       </c>
       <c r="M55">
-        <v>0.5056470300000001</v>
+        <v>0.51518754</v>
       </c>
       <c r="N55">
-        <v>3.01185297</v>
+        <v>3.00231246</v>
       </c>
       <c r="O55">
-        <v>0.8734373612999998</v>
+        <v>0.8706706133999998</v>
       </c>
       <c r="P55">
-        <v>2.1384156087</v>
+        <v>2.1316418466</v>
       </c>
       <c r="Q55">
-        <v>2.7084156087</v>
+        <v>2.7016418466</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2895230572622726</v>
+        <v>0.2939680677852194</v>
       </c>
       <c r="T55">
-        <v>1.490579878419182</v>
+        <v>1.517765009441628</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.956433621295074</v>
+        <v>6.827610776456278</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1560439311812009</v>
+        <v>0.1555789354491337</v>
       </c>
       <c r="C56">
-        <v>12.44157804771453</v>
+        <v>12.35868485294072</v>
       </c>
       <c r="D56">
-        <v>21.91037804771453</v>
+        <v>22.00318485294073</v>
       </c>
       <c r="E56">
-        <v>7.4178</v>
+        <v>7.593500000000001</v>
       </c>
       <c r="F56">
-        <v>9.4878</v>
+        <v>9.663500000000001</v>
       </c>
       <c r="G56">
         <v>0.019</v>
@@ -5861,28 +5861,28 @@
         <v>3.5175</v>
       </c>
       <c r="M56">
-        <v>0.51518754</v>
+        <v>0.5247280500000001</v>
       </c>
       <c r="N56">
-        <v>3.00231246</v>
+        <v>2.992771949999999</v>
       </c>
       <c r="O56">
-        <v>0.8706706133999998</v>
+        <v>0.8679038654999998</v>
       </c>
       <c r="P56">
-        <v>2.1316418466</v>
+        <v>2.1248680845</v>
       </c>
       <c r="Q56">
-        <v>2.7016418466</v>
+        <v>2.694868084499999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2939680677852194</v>
+        <v>0.2986106343314083</v>
       </c>
       <c r="T56">
-        <v>1.517765009441628</v>
+        <v>1.546158368509516</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.827610776456278</v>
+        <v>6.703472398702526</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1555789354491337</v>
+        <v>0.1551139397170665</v>
       </c>
       <c r="C57">
-        <v>12.35868485294072</v>
+        <v>12.27658121471293</v>
       </c>
       <c r="D57">
-        <v>22.00318485294073</v>
+        <v>22.09678121471293</v>
       </c>
       <c r="E57">
-        <v>7.593500000000001</v>
+        <v>7.769200000000001</v>
       </c>
       <c r="F57">
-        <v>9.663500000000001</v>
+        <v>9.839200000000002</v>
       </c>
       <c r="G57">
         <v>0.019</v>
@@ -5943,28 +5943,28 @@
         <v>3.5175</v>
       </c>
       <c r="M57">
-        <v>0.5247280500000001</v>
+        <v>0.5342685600000001</v>
       </c>
       <c r="N57">
-        <v>2.992771949999999</v>
+        <v>2.98323144</v>
       </c>
       <c r="O57">
-        <v>0.8679038654999998</v>
+        <v>0.8651371175999998</v>
       </c>
       <c r="P57">
-        <v>2.1248680845</v>
+        <v>2.1180943224</v>
       </c>
       <c r="Q57">
-        <v>2.694868084499999</v>
+        <v>2.6880943224</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2986106343314083</v>
+        <v>0.3034642266296966</v>
       </c>
       <c r="T57">
-        <v>1.546158368509516</v>
+        <v>1.575842334807762</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.703472398702526</v>
+        <v>6.583767534439981</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1551139397170665</v>
+        <v>0.1546489439849993</v>
       </c>
       <c r="C58">
-        <v>12.27658121471293</v>
+        <v>12.19527725183645</v>
       </c>
       <c r="D58">
-        <v>22.09678121471293</v>
+        <v>22.19117725183645</v>
       </c>
       <c r="E58">
-        <v>7.769200000000001</v>
+        <v>7.944900000000001</v>
       </c>
       <c r="F58">
-        <v>9.839200000000002</v>
+        <v>10.0149</v>
       </c>
       <c r="G58">
         <v>0.019</v>
@@ -6025,28 +6025,28 @@
         <v>3.5175</v>
       </c>
       <c r="M58">
-        <v>0.5342685600000001</v>
+        <v>0.54380907</v>
       </c>
       <c r="N58">
-        <v>2.98323144</v>
+        <v>2.97369093</v>
       </c>
       <c r="O58">
-        <v>0.8651371175999998</v>
+        <v>0.8623703696999998</v>
       </c>
       <c r="P58">
-        <v>2.1180943224</v>
+        <v>2.1113205603</v>
       </c>
       <c r="Q58">
-        <v>2.6880943224</v>
+        <v>2.6813205603</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3034642266296966</v>
+        <v>0.3085435674069752</v>
       </c>
       <c r="T58">
-        <v>1.575842334807762</v>
+        <v>1.606906950701277</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.583767534439981</v>
+        <v>6.468262840853316</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1546489439849993</v>
+        <v>0.1541839482529321</v>
       </c>
       <c r="C59">
-        <v>12.19527725183645</v>
+        <v>12.11478325676598</v>
       </c>
       <c r="D59">
-        <v>22.19117725183645</v>
+        <v>22.28638325676599</v>
       </c>
       <c r="E59">
-        <v>7.944900000000001</v>
+        <v>8.120600000000001</v>
       </c>
       <c r="F59">
-        <v>10.0149</v>
+        <v>10.1906</v>
       </c>
       <c r="G59">
         <v>0.019</v>
@@ -6107,28 +6107,28 @@
         <v>3.5175</v>
       </c>
       <c r="M59">
-        <v>0.54380907</v>
+        <v>0.5533495800000001</v>
       </c>
       <c r="N59">
-        <v>2.97369093</v>
+        <v>2.964150419999999</v>
       </c>
       <c r="O59">
-        <v>0.8623703696999998</v>
+        <v>0.8596036217999997</v>
       </c>
       <c r="P59">
-        <v>2.1113205603</v>
+        <v>2.104546798199999</v>
       </c>
       <c r="Q59">
-        <v>2.6813205603</v>
+        <v>2.674546798199999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3085435674069752</v>
+        <v>0.3138647815546002</v>
       </c>
       <c r="T59">
-        <v>1.606906950701277</v>
+        <v>1.639450834018291</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.468262840853316</v>
+        <v>6.356741067735153</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1541839482529321</v>
+        <v>0.1537189525208649</v>
       </c>
       <c r="C60">
-        <v>12.11478325676599</v>
+        <v>12.03510969934665</v>
       </c>
       <c r="D60">
-        <v>22.28638325676599</v>
+        <v>22.38240969934665</v>
       </c>
       <c r="E60">
-        <v>8.1206</v>
+        <v>8.296299999999999</v>
       </c>
       <c r="F60">
-        <v>10.1906</v>
+        <v>10.3663</v>
       </c>
       <c r="G60">
         <v>0.019</v>
@@ -6189,28 +6189,28 @@
         <v>3.5175</v>
       </c>
       <c r="M60">
-        <v>0.55334958</v>
+        <v>0.56289009</v>
       </c>
       <c r="N60">
-        <v>2.96415042</v>
+        <v>2.954609909999999</v>
       </c>
       <c r="O60">
-        <v>0.8596036217999998</v>
+        <v>0.8568368738999997</v>
       </c>
       <c r="P60">
-        <v>2.1045467982</v>
+        <v>2.0977730361</v>
       </c>
       <c r="Q60">
-        <v>2.6745467982</v>
+        <v>2.667773036099999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3138647815546002</v>
+        <v>0.3194455671240607</v>
       </c>
       <c r="T60">
-        <v>1.639450834018291</v>
+        <v>1.673582223838574</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.356741067735155</v>
+        <v>6.248999693705745</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1537189525208649</v>
+        <v>0.1532539567887977</v>
       </c>
       <c r="C61">
-        <v>12.03510969934665</v>
+        <v>11.9562672306522</v>
       </c>
       <c r="D61">
-        <v>22.38240969934665</v>
+        <v>22.4792672306522</v>
       </c>
       <c r="E61">
-        <v>8.296299999999999</v>
+        <v>8.472</v>
       </c>
       <c r="F61">
-        <v>10.3663</v>
+        <v>10.542</v>
       </c>
       <c r="G61">
         <v>0.019</v>
@@ -6271,28 +6271,28 @@
         <v>3.5175</v>
       </c>
       <c r="M61">
-        <v>0.56289009</v>
+        <v>0.5724306</v>
       </c>
       <c r="N61">
-        <v>2.954609909999999</v>
+        <v>2.9450694</v>
       </c>
       <c r="O61">
-        <v>0.8568368738999997</v>
+        <v>0.8540701259999998</v>
       </c>
       <c r="P61">
-        <v>2.0977730361</v>
+        <v>2.090999274</v>
       </c>
       <c r="Q61">
-        <v>2.667773036099999</v>
+        <v>2.660999273999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3194455671240607</v>
+        <v>0.3253053919719942</v>
       </c>
       <c r="T61">
-        <v>1.673582223838574</v>
+        <v>1.709420183149872</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.248999693705745</v>
+        <v>6.14484969881065</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1532539567887977</v>
+        <v>0.1532220610567304</v>
       </c>
       <c r="C62">
-        <v>11.9562672306522</v>
+        <v>11.78724176917439</v>
       </c>
       <c r="D62">
-        <v>22.4792672306522</v>
+        <v>22.48594176917439</v>
       </c>
       <c r="E62">
-        <v>8.472</v>
+        <v>8.6477</v>
       </c>
       <c r="F62">
-        <v>10.542</v>
+        <v>10.7177</v>
       </c>
       <c r="G62">
         <v>0.019</v>
@@ -6353,45 +6353,45 @@
         <v>3.5175</v>
       </c>
       <c r="M62">
-        <v>0.5724306</v>
+        <v>0.5926888100000001</v>
       </c>
       <c r="N62">
-        <v>2.9450694</v>
+        <v>2.92481119</v>
       </c>
       <c r="O62">
-        <v>0.8540701259999998</v>
+        <v>0.8481952450999999</v>
       </c>
       <c r="P62">
-        <v>2.090999274</v>
+        <v>2.0766159449</v>
       </c>
       <c r="Q62">
-        <v>2.660999273999999</v>
+        <v>2.6466159449</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3253053919719942</v>
+        <v>0.3314657206582832</v>
       </c>
       <c r="T62">
-        <v>1.709420183149872</v>
+        <v>1.747095986528416</v>
       </c>
       <c r="U62">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V62">
         <v>0.29</v>
       </c>
       <c r="W62">
-        <v>0.038553</v>
+        <v>0.039263</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>6.14484969881065</v>
+        <v>5.934817632207363</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1532220610567304</v>
+        <v>0.1527641653246632</v>
       </c>
       <c r="C63">
-        <v>11.78724176917439</v>
+        <v>11.70780033143554</v>
       </c>
       <c r="D63">
-        <v>22.48594176917439</v>
+        <v>22.58220033143554</v>
       </c>
       <c r="E63">
-        <v>8.6477</v>
+        <v>8.823399999999999</v>
       </c>
       <c r="F63">
-        <v>10.7177</v>
+        <v>10.8934</v>
       </c>
       <c r="G63">
         <v>0.019</v>
@@ -6435,28 +6435,28 @@
         <v>3.5175</v>
       </c>
       <c r="M63">
-        <v>0.5926888100000001</v>
+        <v>0.60240502</v>
       </c>
       <c r="N63">
-        <v>2.92481119</v>
+        <v>2.91509498</v>
       </c>
       <c r="O63">
-        <v>0.8481952450999999</v>
+        <v>0.8453775441999999</v>
       </c>
       <c r="P63">
-        <v>2.0766159449</v>
+        <v>2.0697174358</v>
       </c>
       <c r="Q63">
-        <v>2.6466159449</v>
+        <v>2.6397174358</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3314657206582832</v>
+        <v>0.3379502771701665</v>
       </c>
       <c r="T63">
-        <v>1.747095986528416</v>
+        <v>1.786754726926883</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.934817632207363</v>
+        <v>5.839094767171761</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1527641653246632</v>
+        <v>0.152306269592596</v>
       </c>
       <c r="C64">
-        <v>11.70780033143554</v>
+        <v>11.62918657050864</v>
       </c>
       <c r="D64">
-        <v>22.58220033143554</v>
+        <v>22.67928657050864</v>
       </c>
       <c r="E64">
-        <v>8.823399999999999</v>
+        <v>8.9991</v>
       </c>
       <c r="F64">
-        <v>10.8934</v>
+        <v>11.0691</v>
       </c>
       <c r="G64">
         <v>0.019</v>
@@ -6517,28 +6517,28 @@
         <v>3.5175</v>
       </c>
       <c r="M64">
-        <v>0.60240502</v>
+        <v>0.6121212300000001</v>
       </c>
       <c r="N64">
-        <v>2.91509498</v>
+        <v>2.90537877</v>
       </c>
       <c r="O64">
-        <v>0.8453775441999999</v>
+        <v>0.8425598432999998</v>
       </c>
       <c r="P64">
-        <v>2.0697174358</v>
+        <v>2.0628189267</v>
       </c>
       <c r="Q64">
-        <v>2.6397174358</v>
+        <v>2.6328189267</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3379502771701665</v>
+        <v>0.3447853502502596</v>
       </c>
       <c r="T64">
-        <v>1.786754726926883</v>
+        <v>1.828557183022564</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.839094767171761</v>
+        <v>5.746410723248398</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.152306269592596</v>
+        <v>0.1518483738605289</v>
       </c>
       <c r="C65">
-        <v>11.62918657050864</v>
+        <v>11.55141120762399</v>
       </c>
       <c r="D65">
-        <v>22.67928657050864</v>
+        <v>22.77721120762399</v>
       </c>
       <c r="E65">
-        <v>8.9991</v>
+        <v>9.174799999999999</v>
       </c>
       <c r="F65">
-        <v>11.0691</v>
+        <v>11.2448</v>
       </c>
       <c r="G65">
         <v>0.019</v>
@@ -6599,28 +6599,28 @@
         <v>3.5175</v>
       </c>
       <c r="M65">
-        <v>0.6121212300000001</v>
+        <v>0.62183744</v>
       </c>
       <c r="N65">
-        <v>2.90537877</v>
+        <v>2.89566256</v>
       </c>
       <c r="O65">
-        <v>0.8425598432999998</v>
+        <v>0.8397421423999999</v>
       </c>
       <c r="P65">
-        <v>2.0628189267</v>
+        <v>2.0559204176</v>
       </c>
       <c r="Q65">
-        <v>2.6328189267</v>
+        <v>2.6259204176</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3447853502502596</v>
+        <v>0.3520001496125801</v>
       </c>
       <c r="T65">
-        <v>1.828557183022564</v>
+        <v>1.872681997790228</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.746410723248398</v>
+        <v>5.656623055697644</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1518483738605289</v>
+        <v>0.1513904781284616</v>
       </c>
       <c r="C66">
-        <v>11.55141120762399</v>
+        <v>11.47448514998341</v>
       </c>
       <c r="D66">
-        <v>22.77721120762399</v>
+        <v>22.87598514998341</v>
       </c>
       <c r="E66">
-        <v>9.174799999999999</v>
+        <v>9.3505</v>
       </c>
       <c r="F66">
-        <v>11.2448</v>
+        <v>11.4205</v>
       </c>
       <c r="G66">
         <v>0.019</v>
@@ -6681,28 +6681,28 @@
         <v>3.5175</v>
       </c>
       <c r="M66">
-        <v>0.62183744</v>
+        <v>0.6315536500000001</v>
       </c>
       <c r="N66">
-        <v>2.89566256</v>
+        <v>2.885946349999999</v>
       </c>
       <c r="O66">
-        <v>0.8397421423999999</v>
+        <v>0.8369244414999998</v>
       </c>
       <c r="P66">
-        <v>2.0559204176</v>
+        <v>2.049021908499999</v>
       </c>
       <c r="Q66">
-        <v>2.6259204176</v>
+        <v>2.619021908499999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3520001496125801</v>
+        <v>0.3596272232241761</v>
       </c>
       <c r="T66">
-        <v>1.872681997790228</v>
+        <v>1.919328230544616</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.656623055697644</v>
+        <v>5.569598085609986</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1513904781284616</v>
+        <v>0.1509325823963944</v>
       </c>
       <c r="C67">
-        <v>11.47448514998341</v>
+        <v>11.39841949481017</v>
       </c>
       <c r="D67">
-        <v>22.87598514998341</v>
+        <v>22.97561949481017</v>
       </c>
       <c r="E67">
-        <v>9.3505</v>
+        <v>9.526200000000001</v>
       </c>
       <c r="F67">
-        <v>11.4205</v>
+        <v>11.5962</v>
       </c>
       <c r="G67">
         <v>0.019</v>
@@ -6763,28 +6763,28 @@
         <v>3.5175</v>
       </c>
       <c r="M67">
-        <v>0.6315536500000001</v>
+        <v>0.6412698600000001</v>
       </c>
       <c r="N67">
-        <v>2.885946349999999</v>
+        <v>2.87623014</v>
       </c>
       <c r="O67">
-        <v>0.8369244414999998</v>
+        <v>0.8341067405999999</v>
       </c>
       <c r="P67">
-        <v>2.049021908499999</v>
+        <v>2.0421233994</v>
       </c>
       <c r="Q67">
-        <v>2.619021908499999</v>
+        <v>2.6121233994</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3596272232241761</v>
+        <v>0.3677029482246896</v>
       </c>
       <c r="T67">
-        <v>1.919328230544616</v>
+        <v>1.968718359343379</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.569598085609986</v>
+        <v>5.485210235828017</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1509325823963944</v>
+        <v>0.1504746866643272</v>
       </c>
       <c r="C68">
-        <v>11.39841949481017</v>
+        <v>11.32322553350519</v>
       </c>
       <c r="D68">
-        <v>22.97561949481017</v>
+        <v>23.07612553350519</v>
       </c>
       <c r="E68">
-        <v>9.526200000000001</v>
+        <v>9.7019</v>
       </c>
       <c r="F68">
-        <v>11.5962</v>
+        <v>11.7719</v>
       </c>
       <c r="G68">
         <v>0.019</v>
@@ -6845,28 +6845,28 @@
         <v>3.5175</v>
       </c>
       <c r="M68">
-        <v>0.6412698600000001</v>
+        <v>0.6509860700000001</v>
       </c>
       <c r="N68">
-        <v>2.87623014</v>
+        <v>2.86651393</v>
       </c>
       <c r="O68">
-        <v>0.8341067405999999</v>
+        <v>0.8312890396999998</v>
       </c>
       <c r="P68">
-        <v>2.0421233994</v>
+        <v>2.0352248903</v>
       </c>
       <c r="Q68">
-        <v>2.6121233994</v>
+        <v>2.6052248903</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3677029482246896</v>
+        <v>0.3762681111040219</v>
       </c>
       <c r="T68">
-        <v>1.968718359343379</v>
+        <v>2.021101829281462</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.485210235828017</v>
+        <v>5.403341426338046</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1504746866643272</v>
+        <v>0.15001679093226</v>
       </c>
       <c r="C69">
-        <v>11.32322553350519</v>
+        <v>11.2489147559128</v>
       </c>
       <c r="D69">
-        <v>23.07612553350519</v>
+        <v>23.17751475591281</v>
       </c>
       <c r="E69">
-        <v>9.7019</v>
+        <v>9.877600000000001</v>
       </c>
       <c r="F69">
-        <v>11.7719</v>
+        <v>11.9476</v>
       </c>
       <c r="G69">
         <v>0.019</v>
@@ -6927,28 +6927,28 @@
         <v>3.5175</v>
       </c>
       <c r="M69">
-        <v>0.6509860700000001</v>
+        <v>0.6607022800000001</v>
       </c>
       <c r="N69">
-        <v>2.86651393</v>
+        <v>2.856797719999999</v>
       </c>
       <c r="O69">
-        <v>0.8312890396999998</v>
+        <v>0.8284713387999998</v>
       </c>
       <c r="P69">
-        <v>2.0352248903</v>
+        <v>2.028326381199999</v>
       </c>
       <c r="Q69">
-        <v>2.6052248903</v>
+        <v>2.598326381199999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3762681111040219</v>
+        <v>0.3853685966633126</v>
       </c>
       <c r="T69">
-        <v>2.021101829281462</v>
+        <v>2.076759266090674</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.403341426338046</v>
+        <v>5.323880523009545</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.15001679093226</v>
+        <v>0.1495588952001928</v>
       </c>
       <c r="C70">
-        <v>11.2489147559128</v>
+        <v>11.17549885469952</v>
       </c>
       <c r="D70">
-        <v>23.17751475591281</v>
+        <v>23.27979885469952</v>
       </c>
       <c r="E70">
-        <v>9.877600000000001</v>
+        <v>10.0533</v>
       </c>
       <c r="F70">
-        <v>11.9476</v>
+        <v>12.1233</v>
       </c>
       <c r="G70">
         <v>0.019</v>
@@ -7009,28 +7009,28 @@
         <v>3.5175</v>
       </c>
       <c r="M70">
-        <v>0.6607022800000001</v>
+        <v>0.6704184900000001</v>
       </c>
       <c r="N70">
-        <v>2.856797719999999</v>
+        <v>2.84708151</v>
       </c>
       <c r="O70">
-        <v>0.8284713387999998</v>
+        <v>0.8256536378999999</v>
       </c>
       <c r="P70">
-        <v>2.028326381199999</v>
+        <v>2.0214278721</v>
       </c>
       <c r="Q70">
-        <v>2.598326381199999</v>
+        <v>2.5914278721</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3853685966633126</v>
+        <v>0.3950562103232027</v>
       </c>
       <c r="T70">
-        <v>2.076759266090674</v>
+        <v>2.136007505274675</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.323880523009545</v>
+        <v>5.246722834270277</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1495588952001928</v>
+        <v>0.1491009994681256</v>
       </c>
       <c r="C71">
-        <v>11.17549885469952</v>
+        <v>11.10298972984918</v>
       </c>
       <c r="D71">
-        <v>23.27979885469952</v>
+        <v>23.38298972984918</v>
       </c>
       <c r="E71">
-        <v>10.0533</v>
+        <v>10.229</v>
       </c>
       <c r="F71">
-        <v>12.1233</v>
+        <v>12.299</v>
       </c>
       <c r="G71">
         <v>0.019</v>
@@ -7091,28 +7091,28 @@
         <v>3.5175</v>
       </c>
       <c r="M71">
-        <v>0.6704184900000001</v>
+        <v>0.6801347000000001</v>
       </c>
       <c r="N71">
-        <v>2.84708151</v>
+        <v>2.8373653</v>
       </c>
       <c r="O71">
-        <v>0.8256536378999999</v>
+        <v>0.8228359369999998</v>
       </c>
       <c r="P71">
-        <v>2.0214278721</v>
+        <v>2.014529363</v>
       </c>
       <c r="Q71">
-        <v>2.5914278721</v>
+        <v>2.584529363</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3950562103232027</v>
+        <v>0.4053896648937521</v>
       </c>
       <c r="T71">
-        <v>2.136007505274675</v>
+        <v>2.199205627070941</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.246722834270277</v>
+        <v>5.171769650923559</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1491009994681256</v>
+        <v>0.1486431037360584</v>
       </c>
       <c r="C72">
-        <v>11.10298972984918</v>
+        <v>11.03139949327822</v>
       </c>
       <c r="D72">
-        <v>23.38298972984918</v>
+        <v>23.48709949327823</v>
       </c>
       <c r="E72">
-        <v>10.229</v>
+        <v>10.4047</v>
       </c>
       <c r="F72">
-        <v>12.299</v>
+        <v>12.4747</v>
       </c>
       <c r="G72">
         <v>0.019</v>
@@ -7173,28 +7173,28 @@
         <v>3.5175</v>
       </c>
       <c r="M72">
-        <v>0.6801347000000001</v>
+        <v>0.6898509100000001</v>
       </c>
       <c r="N72">
-        <v>2.8373653</v>
+        <v>2.82764909</v>
       </c>
       <c r="O72">
-        <v>0.8228359369999998</v>
+        <v>0.8200182360999998</v>
       </c>
       <c r="P72">
-        <v>2.014529363</v>
+        <v>2.0076308539</v>
       </c>
       <c r="Q72">
-        <v>2.584529363</v>
+        <v>2.5776308539</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4053896648937521</v>
+        <v>0.4164357715036497</v>
       </c>
       <c r="T72">
-        <v>2.199205627070941</v>
+        <v>2.266762240025572</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.171769650923559</v>
+        <v>5.098927824854212</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1486431037360584</v>
+        <v>0.1481852080039912</v>
       </c>
       <c r="C73">
-        <v>11.03139949327822</v>
+        <v>10.96074047357481</v>
       </c>
       <c r="D73">
-        <v>23.48709949327822</v>
+        <v>23.59214047357481</v>
       </c>
       <c r="E73">
-        <v>10.4047</v>
+        <v>10.5804</v>
       </c>
       <c r="F73">
-        <v>12.4747</v>
+        <v>12.6504</v>
       </c>
       <c r="G73">
         <v>0.019</v>
@@ -7255,28 +7255,28 @@
         <v>3.5175</v>
       </c>
       <c r="M73">
-        <v>0.6898509100000001</v>
+        <v>0.69956712</v>
       </c>
       <c r="N73">
-        <v>2.82764909</v>
+        <v>2.81793288</v>
       </c>
       <c r="O73">
-        <v>0.8200182360999998</v>
+        <v>0.8172005351999999</v>
       </c>
       <c r="P73">
-        <v>2.0076308539</v>
+        <v>2.0007323448</v>
       </c>
       <c r="Q73">
-        <v>2.5776308539</v>
+        <v>2.5707323448</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4164357715036496</v>
+        <v>0.42827088572854</v>
       </c>
       <c r="T73">
-        <v>2.266762240025571</v>
+        <v>2.339144325334104</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.098927824854212</v>
+        <v>5.02810938284235</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1481852080039912</v>
+        <v>0.147727312271924</v>
       </c>
       <c r="C74">
-        <v>10.96074047357481</v>
+        <v>10.89102522086571</v>
       </c>
       <c r="D74">
-        <v>23.59214047357481</v>
+        <v>23.69812522086571</v>
       </c>
       <c r="E74">
-        <v>10.5804</v>
+        <v>10.7561</v>
       </c>
       <c r="F74">
-        <v>12.6504</v>
+        <v>12.8261</v>
       </c>
       <c r="G74">
         <v>0.019</v>
@@ -7337,28 +7337,28 @@
         <v>3.5175</v>
       </c>
       <c r="M74">
-        <v>0.69956712</v>
+        <v>0.70928333</v>
       </c>
       <c r="N74">
-        <v>2.81793288</v>
+        <v>2.80821667</v>
       </c>
       <c r="O74">
-        <v>0.8172005351999999</v>
+        <v>0.8143828342999999</v>
       </c>
       <c r="P74">
-        <v>2.0007323448</v>
+        <v>1.9938338357</v>
       </c>
       <c r="Q74">
-        <v>2.5707323448</v>
+        <v>2.5638338357</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.42827088572854</v>
+        <v>0.4409826750811999</v>
       </c>
       <c r="T74">
-        <v>2.339144325334104</v>
+        <v>2.416888046591416</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.02810938284235</v>
+        <v>4.959231172118482</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.147727312271924</v>
+        <v>0.1472694165398568</v>
       </c>
       <c r="C75">
-        <v>10.89102522086571</v>
+        <v>10.82226651181486</v>
       </c>
       <c r="D75">
-        <v>23.69812522086571</v>
+        <v>23.80506651181486</v>
       </c>
       <c r="E75">
-        <v>10.7561</v>
+        <v>10.9318</v>
       </c>
       <c r="F75">
-        <v>12.8261</v>
+        <v>13.0018</v>
       </c>
       <c r="G75">
         <v>0.019</v>
@@ -7419,28 +7419,28 @@
         <v>3.5175</v>
       </c>
       <c r="M75">
-        <v>0.70928333</v>
+        <v>0.71899954</v>
       </c>
       <c r="N75">
-        <v>2.80821667</v>
+        <v>2.79850046</v>
       </c>
       <c r="O75">
-        <v>0.8143828342999999</v>
+        <v>0.8115651333999998</v>
       </c>
       <c r="P75">
-        <v>1.9938338357</v>
+        <v>1.9869353266</v>
       </c>
       <c r="Q75">
-        <v>2.5638338357</v>
+        <v>2.5569353266</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4409826750811999</v>
+        <v>0.4546722943840645</v>
       </c>
       <c r="T75">
-        <v>2.416888046591416</v>
+        <v>2.500612054099291</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.959231172118482</v>
+        <v>4.892214534657422</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1472694165398568</v>
+        <v>0.1468115208077896</v>
       </c>
       <c r="C76">
-        <v>10.82226651181486</v>
+        <v>10.75447735475798</v>
       </c>
       <c r="D76">
-        <v>23.80506651181486</v>
+        <v>23.91297735475798</v>
       </c>
       <c r="E76">
-        <v>10.9318</v>
+        <v>11.1075</v>
       </c>
       <c r="F76">
-        <v>13.0018</v>
+        <v>13.1775</v>
       </c>
       <c r="G76">
         <v>0.019</v>
@@ -7501,28 +7501,28 @@
         <v>3.5175</v>
       </c>
       <c r="M76">
-        <v>0.71899954</v>
+        <v>0.72871575</v>
       </c>
       <c r="N76">
-        <v>2.79850046</v>
+        <v>2.78878425</v>
       </c>
       <c r="O76">
-        <v>0.8115651333999998</v>
+        <v>0.8087474324999998</v>
       </c>
       <c r="P76">
-        <v>1.9869353266</v>
+        <v>1.9800368175</v>
       </c>
       <c r="Q76">
-        <v>2.5569353266</v>
+        <v>2.5500368175</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4546722943840645</v>
+        <v>0.4694570832311583</v>
       </c>
       <c r="T76">
-        <v>2.500612054099291</v>
+        <v>2.591033982207796</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.892214534657422</v>
+        <v>4.826985007528656</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1468115208077896</v>
+        <v>0.1463536250757224</v>
       </c>
       <c r="C77">
-        <v>10.75447735475798</v>
+        <v>10.68767099497749</v>
       </c>
       <c r="D77">
-        <v>23.91297735475798</v>
+        <v>24.02187099497749</v>
       </c>
       <c r="E77">
-        <v>11.1075</v>
+        <v>11.2832</v>
       </c>
       <c r="F77">
-        <v>13.1775</v>
+        <v>13.3532</v>
       </c>
       <c r="G77">
         <v>0.019</v>
@@ -7583,28 +7583,28 @@
         <v>3.5175</v>
       </c>
       <c r="M77">
-        <v>0.72871575</v>
+        <v>0.7384319600000001</v>
       </c>
       <c r="N77">
-        <v>2.78878425</v>
+        <v>2.779068039999999</v>
       </c>
       <c r="O77">
-        <v>0.8087474324999998</v>
+        <v>0.8059297315999998</v>
       </c>
       <c r="P77">
-        <v>1.9800368175</v>
+        <v>1.9731383084</v>
       </c>
       <c r="Q77">
-        <v>2.5500368175</v>
+        <v>2.5431383084</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4694570832311583</v>
+        <v>0.4854739378155098</v>
       </c>
       <c r="T77">
-        <v>2.591033982207796</v>
+        <v>2.68899107099201</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.826985007528656</v>
+        <v>4.763472046903278</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1463536250757224</v>
+        <v>0.1458957293436552</v>
       </c>
       <c r="C78">
-        <v>10.68767099497749</v>
+        <v>10.6218609201221</v>
       </c>
       <c r="D78">
-        <v>24.02187099497749</v>
+        <v>24.1317609201221</v>
       </c>
       <c r="E78">
-        <v>11.2832</v>
+        <v>11.4589</v>
       </c>
       <c r="F78">
-        <v>13.3532</v>
+        <v>13.5289</v>
       </c>
       <c r="G78">
         <v>0.019</v>
@@ -7665,28 +7665,28 @@
         <v>3.5175</v>
       </c>
       <c r="M78">
-        <v>0.7384319600000001</v>
+        <v>0.74814817</v>
       </c>
       <c r="N78">
-        <v>2.779068039999999</v>
+        <v>2.76935183</v>
       </c>
       <c r="O78">
-        <v>0.8059297315999998</v>
+        <v>0.8031120306999999</v>
       </c>
       <c r="P78">
-        <v>1.9731383084</v>
+        <v>1.9662397993</v>
       </c>
       <c r="Q78">
-        <v>2.5431383084</v>
+        <v>2.5362397993</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4854739378155098</v>
+        <v>0.5028835623637181</v>
       </c>
       <c r="T78">
-        <v>2.68899107099201</v>
+        <v>2.795466167496591</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.763472046903278</v>
+        <v>4.701608773566872</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1458957293436552</v>
+        <v>0.1454378336115879</v>
       </c>
       <c r="C79">
-        <v>10.6218609201221</v>
+        <v>10.55706086577593</v>
       </c>
       <c r="D79">
-        <v>24.1317609201221</v>
+        <v>24.24266086577593</v>
       </c>
       <c r="E79">
-        <v>11.4589</v>
+        <v>11.6346</v>
       </c>
       <c r="F79">
-        <v>13.5289</v>
+        <v>13.7046</v>
       </c>
       <c r="G79">
         <v>0.019</v>
@@ -7747,28 +7747,28 @@
         <v>3.5175</v>
       </c>
       <c r="M79">
-        <v>0.74814817</v>
+        <v>0.7578643800000001</v>
       </c>
       <c r="N79">
-        <v>2.76935183</v>
+        <v>2.75963562</v>
       </c>
       <c r="O79">
-        <v>0.8031120306999999</v>
+        <v>0.8002943297999998</v>
       </c>
       <c r="P79">
-        <v>1.9662397993</v>
+        <v>1.9593412902</v>
       </c>
       <c r="Q79">
-        <v>2.5362397993</v>
+        <v>2.5293412902</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5028835623637181</v>
+        <v>0.5218758800526725</v>
       </c>
       <c r="T79">
-        <v>2.795466167496591</v>
+        <v>2.91162081822886</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.701608773566872</v>
+        <v>4.641331738008322</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1454378336115879</v>
+        <v>0.1449799378795207</v>
       </c>
       <c r="C80">
-        <v>10.55706086577593</v>
+        <v>10.49328482118187</v>
       </c>
       <c r="D80">
-        <v>24.24266086577593</v>
+        <v>24.35458482118187</v>
       </c>
       <c r="E80">
-        <v>11.6346</v>
+        <v>11.8103</v>
       </c>
       <c r="F80">
-        <v>13.7046</v>
+        <v>13.8803</v>
       </c>
       <c r="G80">
         <v>0.019</v>
@@ -7829,28 +7829,28 @@
         <v>3.5175</v>
       </c>
       <c r="M80">
-        <v>0.7578643800000001</v>
+        <v>0.76758059</v>
       </c>
       <c r="N80">
-        <v>2.75963562</v>
+        <v>2.74991941</v>
       </c>
       <c r="O80">
-        <v>0.8002943297999998</v>
+        <v>0.7974766288999998</v>
       </c>
       <c r="P80">
-        <v>1.9593412902</v>
+        <v>1.9524427811</v>
       </c>
       <c r="Q80">
-        <v>2.5293412902</v>
+        <v>2.5224427811</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5218758800526725</v>
+        <v>0.5426769899024797</v>
       </c>
       <c r="T80">
-        <v>2.91162081822886</v>
+        <v>3.038837816649917</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.641331738008322</v>
+        <v>4.582580703349989</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1449799378795207</v>
+        <v>0.1445220421474535</v>
       </c>
       <c r="C81">
-        <v>10.49328482118187</v>
+        <v>10.43054703512424</v>
       </c>
       <c r="D81">
-        <v>24.35458482118187</v>
+        <v>24.46754703512424</v>
       </c>
       <c r="E81">
-        <v>11.8103</v>
+        <v>11.986</v>
       </c>
       <c r="F81">
-        <v>13.8803</v>
+        <v>14.056</v>
       </c>
       <c r="G81">
         <v>0.019</v>
@@ -7911,28 +7911,28 @@
         <v>3.5175</v>
       </c>
       <c r="M81">
-        <v>0.76758059</v>
+        <v>0.7772968000000001</v>
       </c>
       <c r="N81">
-        <v>2.74991941</v>
+        <v>2.740203199999999</v>
       </c>
       <c r="O81">
-        <v>0.7974766288999998</v>
+        <v>0.7946589279999998</v>
       </c>
       <c r="P81">
-        <v>1.9524427811</v>
+        <v>1.945544272</v>
       </c>
       <c r="Q81">
-        <v>2.5224427811</v>
+        <v>2.515544272</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5426769899024797</v>
+        <v>0.5655582107372676</v>
       </c>
       <c r="T81">
-        <v>3.038837816649917</v>
+        <v>3.178776514913079</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.582580703349989</v>
+        <v>4.525298444558113</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1445220421474535</v>
+        <v>0.1455018964153863</v>
       </c>
       <c r="C82">
-        <v>10.43054703512424</v>
+        <v>10.01438390202266</v>
       </c>
       <c r="D82">
-        <v>24.46754703512424</v>
+        <v>24.22708390202266</v>
       </c>
       <c r="E82">
-        <v>11.986</v>
+        <v>12.1617</v>
       </c>
       <c r="F82">
-        <v>14.056</v>
+        <v>14.2317</v>
       </c>
       <c r="G82">
         <v>0.019</v>
@@ -7993,45 +7993,45 @@
         <v>3.5175</v>
       </c>
       <c r="M82">
-        <v>0.7772968000000001</v>
+        <v>0.8225922600000002</v>
       </c>
       <c r="N82">
-        <v>2.740203199999999</v>
+        <v>2.69490774</v>
       </c>
       <c r="O82">
-        <v>0.7946589279999998</v>
+        <v>0.7815232445999999</v>
       </c>
       <c r="P82">
-        <v>1.945544272</v>
+        <v>1.9133844954</v>
       </c>
       <c r="Q82">
-        <v>2.515544272</v>
+        <v>2.4833844954</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5655582107372676</v>
+        <v>0.5908479811336123</v>
       </c>
       <c r="T82">
-        <v>3.178776514913079</v>
+        <v>3.333445602467102</v>
       </c>
       <c r="U82">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V82">
         <v>0.29</v>
       </c>
       <c r="W82">
-        <v>0.039263</v>
+        <v>0.041038</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y82">
-        <v>4.525298444558113</v>
+        <v>4.276116091829017</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1455018964153863</v>
+        <v>0.1450617506833191</v>
       </c>
       <c r="C83">
-        <v>10.01438390202266</v>
+        <v>9.946111461042145</v>
       </c>
       <c r="D83">
-        <v>24.22708390202266</v>
+        <v>24.33451146104215</v>
       </c>
       <c r="E83">
-        <v>12.1617</v>
+        <v>12.3374</v>
       </c>
       <c r="F83">
-        <v>14.2317</v>
+        <v>14.4074</v>
       </c>
       <c r="G83">
         <v>0.019</v>
@@ -8075,28 +8075,28 @@
         <v>3.5175</v>
       </c>
       <c r="M83">
-        <v>0.8225922600000002</v>
+        <v>0.8327477200000001</v>
       </c>
       <c r="N83">
-        <v>2.69490774</v>
+        <v>2.68475228</v>
       </c>
       <c r="O83">
-        <v>0.7815232445999999</v>
+        <v>0.7785781611999999</v>
       </c>
       <c r="P83">
-        <v>1.9133844954</v>
+        <v>1.9061741188</v>
       </c>
       <c r="Q83">
-        <v>2.4833844954</v>
+        <v>2.476174118799999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5908479811336123</v>
+        <v>0.6189477260184396</v>
       </c>
       <c r="T83">
-        <v>3.333445602467102</v>
+        <v>3.505300144193793</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.276116091829017</v>
+        <v>4.223968334611591</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1450617506833191</v>
+        <v>0.1446216049512519</v>
       </c>
       <c r="C84">
-        <v>9.946111461042145</v>
+        <v>9.878795972372458</v>
       </c>
       <c r="D84">
-        <v>24.33451146104215</v>
+        <v>24.44289597237246</v>
       </c>
       <c r="E84">
-        <v>12.3374</v>
+        <v>12.5131</v>
       </c>
       <c r="F84">
-        <v>14.4074</v>
+        <v>14.5831</v>
       </c>
       <c r="G84">
         <v>0.019</v>
@@ -8157,28 +8157,28 @@
         <v>3.5175</v>
       </c>
       <c r="M84">
-        <v>0.8327477200000001</v>
+        <v>0.8429031800000002</v>
       </c>
       <c r="N84">
-        <v>2.68475228</v>
+        <v>2.67459682</v>
       </c>
       <c r="O84">
-        <v>0.7785781611999999</v>
+        <v>0.7756330777999998</v>
       </c>
       <c r="P84">
-        <v>1.9061741188</v>
+        <v>1.8989637422</v>
       </c>
       <c r="Q84">
-        <v>2.476174118799999</v>
+        <v>2.4689637422</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6189477260184396</v>
+        <v>0.6503533232426584</v>
       </c>
       <c r="T84">
-        <v>3.505300144193793</v>
+        <v>3.697372867300095</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.223968334611591</v>
+        <v>4.173077149857233</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1446216049512519</v>
+        <v>0.1441814592191847</v>
       </c>
       <c r="C85">
-        <v>9.878795972372458</v>
+        <v>9.81245027985058</v>
       </c>
       <c r="D85">
-        <v>24.44289597237246</v>
+        <v>24.55225027985058</v>
       </c>
       <c r="E85">
-        <v>12.5131</v>
+        <v>12.6888</v>
       </c>
       <c r="F85">
-        <v>14.5831</v>
+        <v>14.7588</v>
       </c>
       <c r="G85">
         <v>0.019</v>
@@ -8239,28 +8239,28 @@
         <v>3.5175</v>
       </c>
       <c r="M85">
-        <v>0.8429031800000002</v>
+        <v>0.8530586400000001</v>
       </c>
       <c r="N85">
-        <v>2.67459682</v>
+        <v>2.66444136</v>
       </c>
       <c r="O85">
-        <v>0.7756330777999998</v>
+        <v>0.7726879943999998</v>
       </c>
       <c r="P85">
-        <v>1.8989637422</v>
+        <v>1.8917533656</v>
       </c>
       <c r="Q85">
-        <v>2.4689637422</v>
+        <v>2.4617533656</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6503533232426584</v>
+        <v>0.6856846201199047</v>
       </c>
       <c r="T85">
-        <v>3.697372867300095</v>
+        <v>3.913454680794685</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.173077149857233</v>
+        <v>4.123397659977981</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1441814592191847</v>
+        <v>0.1437413134871175</v>
       </c>
       <c r="C86">
-        <v>9.812450279850582</v>
+        <v>9.74708745819304</v>
       </c>
       <c r="D86">
-        <v>24.55225027985058</v>
+        <v>24.66258745819304</v>
       </c>
       <c r="E86">
-        <v>12.6888</v>
+        <v>12.8645</v>
       </c>
       <c r="F86">
-        <v>14.7588</v>
+        <v>14.9345</v>
       </c>
       <c r="G86">
         <v>0.019</v>
@@ -8321,28 +8321,28 @@
         <v>3.5175</v>
       </c>
       <c r="M86">
-        <v>0.85305864</v>
+        <v>0.8632141000000001</v>
       </c>
       <c r="N86">
-        <v>2.66444136</v>
+        <v>2.6542859</v>
       </c>
       <c r="O86">
-        <v>0.7726879943999998</v>
+        <v>0.7697429109999998</v>
       </c>
       <c r="P86">
-        <v>1.8917533656</v>
+        <v>1.884542989</v>
       </c>
       <c r="Q86">
-        <v>2.4617533656</v>
+        <v>2.454542989</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6856846201199043</v>
+        <v>0.7257267565807831</v>
       </c>
       <c r="T86">
-        <v>3.913454680794682</v>
+        <v>4.158347402755217</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.123397659977982</v>
+        <v>4.074887099272358</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1437413134871175</v>
+        <v>0.1433011677550503</v>
       </c>
       <c r="C87">
-        <v>9.74708745819304</v>
+        <v>9.682720818207033</v>
       </c>
       <c r="D87">
-        <v>24.66258745819304</v>
+        <v>24.77392081820703</v>
       </c>
       <c r="E87">
-        <v>12.8645</v>
+        <v>13.0402</v>
       </c>
       <c r="F87">
-        <v>14.9345</v>
+        <v>15.1102</v>
       </c>
       <c r="G87">
         <v>0.019</v>
@@ -8403,28 +8403,28 @@
         <v>3.5175</v>
       </c>
       <c r="M87">
-        <v>0.8632141000000001</v>
+        <v>0.8733695600000001</v>
       </c>
       <c r="N87">
-        <v>2.6542859</v>
+        <v>2.64413044</v>
       </c>
       <c r="O87">
-        <v>0.7697429109999998</v>
+        <v>0.7667978275999998</v>
       </c>
       <c r="P87">
-        <v>1.884542989</v>
+        <v>1.8773326124</v>
       </c>
       <c r="Q87">
-        <v>2.454542989</v>
+        <v>2.447332612399999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7257267565807831</v>
+        <v>0.7714891982503591</v>
       </c>
       <c r="T87">
-        <v>4.158347402755217</v>
+        <v>4.438224799281542</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.074887099272358</v>
+        <v>4.027504691141284</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1433011677550503</v>
+        <v>0.1450229720229831</v>
       </c>
       <c r="C88">
-        <v>9.682720818207033</v>
+        <v>9.07712195780667</v>
       </c>
       <c r="D88">
-        <v>24.77392081820703</v>
+        <v>24.34402195780667</v>
       </c>
       <c r="E88">
-        <v>13.0402</v>
+        <v>13.2159</v>
       </c>
       <c r="F88">
-        <v>15.1102</v>
+        <v>15.2859</v>
       </c>
       <c r="G88">
         <v>0.019</v>
@@ -8485,45 +8485,45 @@
         <v>3.5175</v>
       </c>
       <c r="M88">
-        <v>0.8733695600000001</v>
+        <v>0.93702567</v>
       </c>
       <c r="N88">
-        <v>2.64413044</v>
+        <v>2.580474329999999</v>
       </c>
       <c r="O88">
-        <v>0.7667978275999998</v>
+        <v>0.7483375556999998</v>
       </c>
       <c r="P88">
-        <v>1.8773326124</v>
+        <v>1.8321367743</v>
       </c>
       <c r="Q88">
-        <v>2.447332612399999</v>
+        <v>2.4021367743</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7714891982503591</v>
+        <v>0.8242920155614081</v>
       </c>
       <c r="T88">
-        <v>4.438224799281542</v>
+        <v>4.761160256811917</v>
       </c>
       <c r="U88">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V88">
         <v>0.29</v>
       </c>
       <c r="W88">
-        <v>0.041038</v>
+        <v>0.043523</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>4.027504691141284</v>
+        <v>3.753899292855018</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1450229720229831</v>
+        <v>0.1446076762909159</v>
       </c>
       <c r="C89">
-        <v>9.07712195780667</v>
+        <v>9.003741623645798</v>
       </c>
       <c r="D89">
-        <v>24.34402195780667</v>
+        <v>24.4463416236458</v>
       </c>
       <c r="E89">
-        <v>13.2159</v>
+        <v>13.3916</v>
       </c>
       <c r="F89">
-        <v>15.2859</v>
+        <v>15.4616</v>
       </c>
       <c r="G89">
         <v>0.019</v>
@@ -8567,28 +8567,28 @@
         <v>3.5175</v>
       </c>
       <c r="M89">
-        <v>0.93702567</v>
+        <v>0.94779608</v>
       </c>
       <c r="N89">
-        <v>2.580474329999999</v>
+        <v>2.569703919999999</v>
       </c>
       <c r="O89">
-        <v>0.7483375556999998</v>
+        <v>0.7452141367999998</v>
       </c>
       <c r="P89">
-        <v>1.8321367743</v>
+        <v>1.8244897832</v>
       </c>
       <c r="Q89">
-        <v>2.4021367743</v>
+        <v>2.394489783199999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8242920155614081</v>
+        <v>0.8858953024242989</v>
       </c>
       <c r="T89">
-        <v>4.761160256811917</v>
+        <v>5.137918290597356</v>
       </c>
       <c r="U89">
         <v>0.0613</v>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.753899292855018</v>
+        <v>3.711241346345302</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1446076762909159</v>
+        <v>0.1441923805588487</v>
       </c>
       <c r="C90">
-        <v>9.003741623645798</v>
+        <v>8.931225033614059</v>
       </c>
       <c r="D90">
-        <v>24.4463416236458</v>
+        <v>24.54952503361406</v>
       </c>
       <c r="E90">
-        <v>13.3916</v>
+        <v>13.5673</v>
       </c>
       <c r="F90">
-        <v>15.4616</v>
+        <v>15.6373</v>
       </c>
       <c r="G90">
         <v>0.019</v>
@@ -8649,28 +8649,28 @@
         <v>3.5175</v>
       </c>
       <c r="M90">
-        <v>0.94779608</v>
+        <v>0.9585664899999999</v>
       </c>
       <c r="N90">
-        <v>2.569703919999999</v>
+        <v>2.55893351</v>
       </c>
       <c r="O90">
-        <v>0.7452141367999998</v>
+        <v>0.7420907178999998</v>
       </c>
       <c r="P90">
-        <v>1.8244897832</v>
+        <v>1.8168427921</v>
       </c>
       <c r="Q90">
-        <v>2.394489783199999</v>
+        <v>2.386842792099999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8858953024242989</v>
+        <v>0.9586991868986243</v>
       </c>
       <c r="T90">
-        <v>5.137918290597356</v>
+        <v>5.583177785071055</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.711241346345302</v>
+        <v>3.66954200537513</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1441923805588487</v>
+        <v>0.1437770848267815</v>
       </c>
       <c r="C91">
-        <v>8.931225033614059</v>
+        <v>8.859583171175112</v>
       </c>
       <c r="D91">
-        <v>24.54952503361406</v>
+        <v>24.65358317117511</v>
       </c>
       <c r="E91">
-        <v>13.5673</v>
+        <v>13.743</v>
       </c>
       <c r="F91">
-        <v>15.6373</v>
+        <v>15.813</v>
       </c>
       <c r="G91">
         <v>0.019</v>
@@ -8731,28 +8731,28 @@
         <v>3.5175</v>
       </c>
       <c r="M91">
-        <v>0.9585664899999999</v>
+        <v>0.9693369000000001</v>
       </c>
       <c r="N91">
-        <v>2.55893351</v>
+        <v>2.5481631</v>
       </c>
       <c r="O91">
-        <v>0.7420907178999998</v>
+        <v>0.7389672989999998</v>
       </c>
       <c r="P91">
-        <v>1.8168427921</v>
+        <v>1.809195801</v>
       </c>
       <c r="Q91">
-        <v>2.386842792099999</v>
+        <v>2.379195801</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9586991868986243</v>
+        <v>1.046063848267815</v>
       </c>
       <c r="T91">
-        <v>5.583177785071055</v>
+        <v>6.117489178439494</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.66954200537513</v>
+        <v>3.628769316426518</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1437770848267815</v>
+        <v>0.1433617890947143</v>
       </c>
       <c r="C92">
-        <v>8.859583171175112</v>
+        <v>8.788827206807891</v>
       </c>
       <c r="D92">
-        <v>24.65358317117511</v>
+        <v>24.75852720680789</v>
       </c>
       <c r="E92">
-        <v>13.743</v>
+        <v>13.9187</v>
       </c>
       <c r="F92">
-        <v>15.813</v>
+        <v>15.9887</v>
       </c>
       <c r="G92">
         <v>0.019</v>
@@ -8813,28 +8813,28 @@
         <v>3.5175</v>
       </c>
       <c r="M92">
-        <v>0.9693369000000001</v>
+        <v>0.9801073100000001</v>
       </c>
       <c r="N92">
-        <v>2.5481631</v>
+        <v>2.537392689999999</v>
       </c>
       <c r="O92">
-        <v>0.7389672989999998</v>
+        <v>0.7358438800999998</v>
       </c>
       <c r="P92">
-        <v>1.809195801</v>
+        <v>1.8015488099</v>
       </c>
       <c r="Q92">
-        <v>2.379195801</v>
+        <v>2.371548809899999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.046063848267815</v>
+        <v>1.152842878830159</v>
       </c>
       <c r="T92">
-        <v>6.117489178439494</v>
+        <v>6.770536437000922</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.628769316426518</v>
+        <v>3.58889273053172</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1433617890947143</v>
+        <v>0.1429464933626471</v>
       </c>
       <c r="C93">
-        <v>8.788827206807891</v>
+        <v>8.718968502003939</v>
       </c>
       <c r="D93">
-        <v>24.75852720680789</v>
+        <v>24.86436850200394</v>
       </c>
       <c r="E93">
-        <v>13.9187</v>
+        <v>14.0944</v>
       </c>
       <c r="F93">
-        <v>15.9887</v>
+        <v>16.1644</v>
       </c>
       <c r="G93">
         <v>0.019</v>
@@ -8895,28 +8895,28 @@
         <v>3.5175</v>
       </c>
       <c r="M93">
-        <v>0.9801073100000001</v>
+        <v>0.9908777200000001</v>
       </c>
       <c r="N93">
-        <v>2.537392689999999</v>
+        <v>2.52662228</v>
       </c>
       <c r="O93">
-        <v>0.7358438800999998</v>
+        <v>0.7327204611999999</v>
       </c>
       <c r="P93">
-        <v>1.8015488099</v>
+        <v>1.7939018188</v>
       </c>
       <c r="Q93">
-        <v>2.371548809899999</v>
+        <v>2.3639018188</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.152842878830159</v>
+        <v>1.286316667033089</v>
       </c>
       <c r="T93">
-        <v>6.770536437000922</v>
+        <v>7.586845510202704</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.58889273053172</v>
+        <v>3.549883026938985</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1429464933626471</v>
+        <v>0.1425311976305798</v>
       </c>
       <c r="C94">
-        <v>8.718968502003939</v>
+        <v>8.650018613367859</v>
       </c>
       <c r="D94">
-        <v>24.86436850200394</v>
+        <v>24.97111861336786</v>
       </c>
       <c r="E94">
-        <v>14.0944</v>
+        <v>14.2701</v>
       </c>
       <c r="F94">
-        <v>16.1644</v>
+        <v>16.3401</v>
       </c>
       <c r="G94">
         <v>0.019</v>
@@ -8977,28 +8977,28 @@
         <v>3.5175</v>
       </c>
       <c r="M94">
-        <v>0.9908777200000001</v>
+        <v>1.00164813</v>
       </c>
       <c r="N94">
-        <v>2.52662228</v>
+        <v>2.51585187</v>
       </c>
       <c r="O94">
-        <v>0.7327204611999999</v>
+        <v>0.7295970422999999</v>
       </c>
       <c r="P94">
-        <v>1.7939018188</v>
+        <v>1.7862548277</v>
       </c>
       <c r="Q94">
-        <v>2.3639018188</v>
+        <v>2.356254827699999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.286316667033089</v>
+        <v>1.457925823293998</v>
       </c>
       <c r="T94">
-        <v>7.586845510202704</v>
+        <v>8.636385747176424</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.549883026938985</v>
+        <v>3.511712241703082</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1425311976305798</v>
+        <v>0.1439846218985126</v>
       </c>
       <c r="C95">
-        <v>8.650018613367859</v>
+        <v>8.104671828684893</v>
       </c>
       <c r="D95">
-        <v>24.97111861336786</v>
+        <v>24.6014718286849</v>
       </c>
       <c r="E95">
-        <v>14.2701</v>
+        <v>14.4458</v>
       </c>
       <c r="F95">
-        <v>16.3401</v>
+        <v>16.5158</v>
       </c>
       <c r="G95">
         <v>0.019</v>
@@ -9059,45 +9059,45 @@
         <v>3.5175</v>
       </c>
       <c r="M95">
-        <v>1.00164813</v>
+        <v>1.05866278</v>
       </c>
       <c r="N95">
-        <v>2.51585187</v>
+        <v>2.458837219999999</v>
       </c>
       <c r="O95">
-        <v>0.7295970422999999</v>
+        <v>0.7130627937999998</v>
       </c>
       <c r="P95">
-        <v>1.7862548277</v>
+        <v>1.7457744262</v>
       </c>
       <c r="Q95">
-        <v>2.356254827699999</v>
+        <v>2.3157744262</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.457925823293998</v>
+        <v>1.686738031641879</v>
       </c>
       <c r="T95">
-        <v>8.636385747176424</v>
+        <v>10.03577272980806</v>
       </c>
       <c r="U95">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V95">
         <v>0.29</v>
       </c>
       <c r="W95">
-        <v>0.043523</v>
+        <v>0.045511</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y95">
-        <v>3.511712241703082</v>
+        <v>3.322587764916038</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1439846218985126</v>
+        <v>0.1435892061664454</v>
       </c>
       <c r="C96">
-        <v>8.104671828684893</v>
+        <v>8.028449157261552</v>
       </c>
       <c r="D96">
-        <v>24.6014718286849</v>
+        <v>24.70094915726155</v>
       </c>
       <c r="E96">
-        <v>14.4458</v>
+        <v>14.6215</v>
       </c>
       <c r="F96">
-        <v>16.5158</v>
+        <v>16.6915</v>
       </c>
       <c r="G96">
         <v>0.019</v>
@@ -9141,28 +9141,28 @@
         <v>3.5175</v>
       </c>
       <c r="M96">
-        <v>1.05866278</v>
+        <v>1.06992515</v>
       </c>
       <c r="N96">
-        <v>2.458837219999999</v>
+        <v>2.44757485</v>
       </c>
       <c r="O96">
-        <v>0.7130627937999998</v>
+        <v>0.7097967064999998</v>
       </c>
       <c r="P96">
-        <v>1.7457744262</v>
+        <v>1.7377781435</v>
       </c>
       <c r="Q96">
-        <v>2.3157744262</v>
+        <v>2.3077781435</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.686738031641879</v>
+        <v>2.007075123328911</v>
       </c>
       <c r="T96">
-        <v>10.03577272980806</v>
+        <v>11.99491450549234</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.322587764916038</v>
+        <v>3.28761315686429</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1435892061664454</v>
+        <v>0.1431937904343782</v>
       </c>
       <c r="C97">
-        <v>8.028449157261552</v>
+        <v>7.953034235501267</v>
       </c>
       <c r="D97">
-        <v>24.70094915726155</v>
+        <v>24.80123423550127</v>
       </c>
       <c r="E97">
-        <v>14.6215</v>
+        <v>14.7972</v>
       </c>
       <c r="F97">
-        <v>16.6915</v>
+        <v>16.8672</v>
       </c>
       <c r="G97">
         <v>0.019</v>
@@ -9223,28 +9223,28 @@
         <v>3.5175</v>
       </c>
       <c r="M97">
-        <v>1.06992515</v>
+        <v>1.08118752</v>
       </c>
       <c r="N97">
-        <v>2.44757485</v>
+        <v>2.43631248</v>
       </c>
       <c r="O97">
-        <v>0.7097967064999998</v>
+        <v>0.7065306191999999</v>
       </c>
       <c r="P97">
-        <v>1.7377781435</v>
+        <v>1.7297818608</v>
       </c>
       <c r="Q97">
-        <v>2.3077781435</v>
+        <v>2.2997818608</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.007075123328911</v>
+        <v>2.487580760859459</v>
       </c>
       <c r="T97">
-        <v>11.99491450549234</v>
+        <v>14.93362716901876</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.28761315686429</v>
+        <v>3.253367186480288</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1431937904343782</v>
+        <v>0.142798374702311</v>
       </c>
       <c r="C98">
-        <v>7.953034235501264</v>
+        <v>7.878436941824937</v>
       </c>
       <c r="D98">
-        <v>24.80123423550127</v>
+        <v>24.90233694182494</v>
       </c>
       <c r="E98">
-        <v>14.7972</v>
+        <v>14.9729</v>
       </c>
       <c r="F98">
-        <v>16.8672</v>
+        <v>17.0429</v>
       </c>
       <c r="G98">
         <v>0.019</v>
@@ -9305,28 +9305,28 @@
         <v>3.5175</v>
       </c>
       <c r="M98">
-        <v>1.08118752</v>
+        <v>1.09244989</v>
       </c>
       <c r="N98">
-        <v>2.43631248</v>
+        <v>2.425050109999999</v>
       </c>
       <c r="O98">
-        <v>0.7065306191999999</v>
+        <v>0.7032645318999998</v>
       </c>
       <c r="P98">
-        <v>1.7297818608</v>
+        <v>1.7217855781</v>
       </c>
       <c r="Q98">
-        <v>2.2997818608</v>
+        <v>2.291785578099999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.487580760859453</v>
+        <v>3.28842349007703</v>
       </c>
       <c r="T98">
-        <v>14.93362716901872</v>
+        <v>19.83148160822941</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.253367186480288</v>
+        <v>3.219827318578429</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.142798374702311</v>
+        <v>0.1424029589702438</v>
       </c>
       <c r="C99">
-        <v>7.878436941824937</v>
+        <v>7.80466731639109</v>
       </c>
       <c r="D99">
-        <v>24.90233694182494</v>
+        <v>25.00426731639109</v>
       </c>
       <c r="E99">
-        <v>14.9729</v>
+        <v>15.1486</v>
       </c>
       <c r="F99">
-        <v>17.0429</v>
+        <v>17.2186</v>
       </c>
       <c r="G99">
         <v>0.019</v>
@@ -9387,28 +9387,28 @@
         <v>3.5175</v>
       </c>
       <c r="M99">
-        <v>1.09244989</v>
+        <v>1.10371226</v>
       </c>
       <c r="N99">
-        <v>2.425050109999999</v>
+        <v>2.41378774</v>
       </c>
       <c r="O99">
-        <v>0.7032645318999998</v>
+        <v>0.6999984445999998</v>
       </c>
       <c r="P99">
-        <v>1.7217855781</v>
+        <v>1.7137892954</v>
       </c>
       <c r="Q99">
-        <v>2.291785578099999</v>
+        <v>2.2837892954</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.28842349007703</v>
+        <v>4.890108948512186</v>
       </c>
       <c r="T99">
-        <v>19.83148160822941</v>
+        <v>29.62719048665079</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.219827318578429</v>
+        <v>3.186971937776608</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1424029589702438</v>
+        <v>0.1420075432381766</v>
       </c>
       <c r="C100">
-        <v>7.80466731639109</v>
+        <v>7.731735564419605</v>
       </c>
       <c r="D100">
-        <v>25.00426731639109</v>
+        <v>25.10703556441961</v>
       </c>
       <c r="E100">
-        <v>15.1486</v>
+        <v>15.3243</v>
       </c>
       <c r="F100">
-        <v>17.2186</v>
+        <v>17.3943</v>
       </c>
       <c r="G100">
         <v>0.019</v>
@@ -9469,28 +9469,28 @@
         <v>3.5175</v>
       </c>
       <c r="M100">
-        <v>1.10371226</v>
+        <v>1.11497463</v>
       </c>
       <c r="N100">
-        <v>2.41378774</v>
+        <v>2.402525369999999</v>
       </c>
       <c r="O100">
-        <v>0.6999984445999998</v>
+        <v>0.6967323572999997</v>
       </c>
       <c r="P100">
-        <v>1.7137892954</v>
+        <v>1.7057930127</v>
       </c>
       <c r="Q100">
-        <v>2.2837892954</v>
+        <v>2.275793012699999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.890108948512186</v>
+        <v>9.695165323817649</v>
       </c>
       <c r="T100">
-        <v>29.62719048665079</v>
+        <v>59.0143171219149</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.186971937776608</v>
+        <v>3.154780302041491</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1420075432381766</v>
-      </c>
-      <c r="C101">
-        <v>7.731735564419605</v>
-      </c>
-      <c r="D101">
-        <v>25.10703556441961</v>
-      </c>
-      <c r="E101">
-        <v>15.3243</v>
-      </c>
-      <c r="F101">
-        <v>17.3943</v>
-      </c>
-      <c r="G101">
-        <v>0.019</v>
-      </c>
-      <c r="H101">
-        <v>15.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.087499999999999</v>
-      </c>
-      <c r="K101">
-        <v>0.5699999999999998</v>
-      </c>
-      <c r="L101">
-        <v>3.5175</v>
-      </c>
-      <c r="M101">
-        <v>1.11497463</v>
-      </c>
-      <c r="N101">
-        <v>2.402525369999999</v>
-      </c>
-      <c r="O101">
-        <v>0.6967323572999997</v>
-      </c>
-      <c r="P101">
-        <v>1.7057930127</v>
-      </c>
-      <c r="Q101">
-        <v>2.275793012699999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.695165323817649</v>
-      </c>
-      <c r="T101">
-        <v>59.0143171219149</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.29</v>
-      </c>
-      <c r="W101">
-        <v>0.045511</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.154780302041491</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
